--- a/自研流变仪材料测试数据.xlsx
+++ b/自研流变仪材料测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Desktop\博士\huawei\交付流变仪\自研流变仪测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B403B0-69C2-4A9D-B6DB-1F1B85489842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04038A5E-AD2D-450C-B8C8-920448B6E696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="94">
   <si>
     <t>平行杆</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -328,6 +328,51 @@
   </si>
   <si>
     <t>DKN7500-XD05-STBC-XD30-92-1 8 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ05-STBC-FeC2-92-0.4 6.6 3</t>
+  </si>
+  <si>
+    <t>c36</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c38</t>
+  </si>
+  <si>
+    <t>c39</t>
+  </si>
+  <si>
+    <t>0520</t>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-90-0.4 8.6 1</t>
+  </si>
+  <si>
+    <t>c37</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-90-0.4 8.6 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-91-0.4 8.6 1</t>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-91-0.4 8.6 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-92-0.4 8.6 1</t>
+  </si>
+  <si>
+    <t>DKN5000-XD05-STBC-XD30-92-0.4 8.6 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0520</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1065,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="39.875" customWidth="1"/>
@@ -1128,7 +1173,7 @@
         <v>69</v>
       </c>
       <c r="H2" s="10">
-        <f>G2/1000*0.318319</f>
+        <f t="shared" ref="H2:H33" si="0">G2/1000*0.318319</f>
         <v>2.1964011000000002E-2</v>
       </c>
       <c r="I2" s="11" t="s">
@@ -1158,7 +1203,7 @@
         <v>111</v>
       </c>
       <c r="H3" s="10">
-        <f>G3/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>3.5333409000000003E-2</v>
       </c>
       <c r="I3" s="11" t="s">
@@ -1188,7 +1233,7 @@
         <v>271</v>
       </c>
       <c r="H4" s="10">
-        <f>G4/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>8.6264449000000007E-2</v>
       </c>
       <c r="I4" s="11" t="s">
@@ -1218,7 +1263,7 @@
         <v>394</v>
       </c>
       <c r="H5" s="10">
-        <f>G5/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.125417686</v>
       </c>
       <c r="I5" s="11" t="s">
@@ -1248,7 +1293,7 @@
         <v>435</v>
       </c>
       <c r="H6" s="10">
-        <f>G6/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.13846876499999999</v>
       </c>
       <c r="I6" s="11" t="s">
@@ -1278,7 +1323,7 @@
         <v>480</v>
       </c>
       <c r="H7" s="10">
-        <f>G7/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.15279312</v>
       </c>
       <c r="I7" s="11" t="s">
@@ -1308,7 +1353,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="22">
-        <f>G8/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>3.1831900000000003E-2</v>
       </c>
       <c r="I8" s="23" t="s">
@@ -1338,7 +1383,7 @@
         <v>244</v>
       </c>
       <c r="H9" s="22">
-        <f>G9/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>7.7669836000000006E-2</v>
       </c>
       <c r="I9" s="23" t="s">
@@ -1368,7 +1413,7 @@
         <v>526</v>
       </c>
       <c r="H10" s="22">
-        <f>G10/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.16743579400000003</v>
       </c>
       <c r="I10" s="23" t="s">
@@ -1398,7 +1443,7 @@
         <v>707</v>
       </c>
       <c r="H11" s="22">
-        <f>G11/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.225051533</v>
       </c>
       <c r="I11" s="23" t="s">
@@ -1428,7 +1473,7 @@
         <v>809</v>
       </c>
       <c r="H12" s="22">
-        <f>G12/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.25752007100000002</v>
       </c>
       <c r="I12" s="23" t="s">
@@ -1458,7 +1503,7 @@
         <v>894</v>
       </c>
       <c r="H13" s="22">
-        <f>G13/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.28457718600000004</v>
       </c>
       <c r="I13" s="23" t="s">
@@ -1488,7 +1533,7 @@
         <v>85</v>
       </c>
       <c r="H14" s="16">
-        <f>G14/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>2.7057115000000003E-2</v>
       </c>
       <c r="I14" s="17" t="s">
@@ -1518,7 +1563,7 @@
         <v>116</v>
       </c>
       <c r="H15" s="16">
-        <f>G15/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>3.6925004000000004E-2</v>
       </c>
       <c r="I15" s="17" t="s">
@@ -1548,7 +1593,7 @@
         <v>413</v>
       </c>
       <c r="H16" s="16">
-        <f>G16/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.13146574699999999</v>
       </c>
       <c r="I16" s="17" t="s">
@@ -1578,7 +1623,7 @@
         <v>676</v>
       </c>
       <c r="H17" s="16">
-        <f>G17/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.21518364400000004</v>
       </c>
       <c r="I17" s="17" t="s">
@@ -1608,7 +1653,7 @@
         <v>785</v>
       </c>
       <c r="H18" s="16">
-        <f>G18/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.24988041500000002</v>
       </c>
       <c r="I18" s="17" t="s">
@@ -1638,7 +1683,7 @@
         <v>850</v>
       </c>
       <c r="H19" s="16">
-        <f>G19/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.27057114999999998</v>
       </c>
       <c r="I19" s="17" t="s">
@@ -1668,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="H20" s="35">
-        <f>G20/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>2.5465520000000001E-3</v>
       </c>
       <c r="I20" s="36" t="s">
@@ -1698,7 +1743,7 @@
         <v>44</v>
       </c>
       <c r="H21" s="35">
-        <f>G21/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>1.4006035999999999E-2</v>
       </c>
       <c r="I21" s="36" t="s">
@@ -1728,7 +1773,7 @@
         <v>317</v>
       </c>
       <c r="H22" s="35">
-        <f>G22/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.100907123</v>
       </c>
       <c r="I22" s="36" t="s">
@@ -1758,7 +1803,7 @@
         <v>465</v>
       </c>
       <c r="H23" s="35">
-        <f>G23/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.14801833500000003</v>
       </c>
       <c r="I23" s="36" t="s">
@@ -1788,7 +1833,7 @@
         <v>531</v>
       </c>
       <c r="H24" s="35">
-        <f>G24/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.16902738900000003</v>
       </c>
       <c r="I24" s="36" t="s">
@@ -1818,7 +1863,7 @@
         <v>576</v>
       </c>
       <c r="H25" s="35">
-        <f>G25/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.18335174399999998</v>
       </c>
       <c r="I25" s="36" t="s">
@@ -1848,7 +1893,7 @@
         <v>15</v>
       </c>
       <c r="H26" s="10">
-        <f>G26/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>4.7747850000000001E-3</v>
       </c>
       <c r="I26" s="11" t="s">
@@ -1878,7 +1923,7 @@
         <v>277</v>
       </c>
       <c r="H27" s="10">
-        <f>G27/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>8.8174363000000019E-2</v>
       </c>
       <c r="I27" s="11" t="s">
@@ -1908,7 +1953,7 @@
         <v>544</v>
       </c>
       <c r="H28" s="10">
-        <f>G28/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.17316553600000001</v>
       </c>
       <c r="I28" s="11" t="s">
@@ -1938,7 +1983,7 @@
         <v>701</v>
       </c>
       <c r="H29" s="10">
-        <f>G29/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.22314161899999999</v>
       </c>
       <c r="I29" s="11" t="s">
@@ -1968,7 +2013,7 @@
         <v>755</v>
       </c>
       <c r="H30" s="10">
-        <f>G30/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.24033084500000002</v>
       </c>
       <c r="I30" s="11" t="s">
@@ -1998,7 +2043,7 @@
         <v>799</v>
       </c>
       <c r="H31" s="10">
-        <f>G31/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>0.25433688100000001</v>
       </c>
       <c r="I31" s="11" t="s">
@@ -2028,7 +2073,7 @@
         <v>-33</v>
       </c>
       <c r="H32" s="22">
-        <f>G32/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>-1.0504527000000001E-2</v>
       </c>
       <c r="I32" s="23" t="s">
@@ -2058,7 +2103,7 @@
         <v>311</v>
       </c>
       <c r="H33" s="22">
-        <f>G33/1000*0.318319</f>
+        <f t="shared" si="0"/>
         <v>9.8997209000000003E-2</v>
       </c>
       <c r="I33" s="23" t="s">
@@ -2088,7 +2133,7 @@
         <v>616</v>
       </c>
       <c r="H34" s="22">
-        <f>G34/1000*0.318319</f>
+        <f t="shared" ref="H34:H65" si="1">G34/1000*0.318319</f>
         <v>0.19608450400000002</v>
       </c>
       <c r="I34" s="23" t="s">
@@ -2118,7 +2163,7 @@
         <v>899</v>
       </c>
       <c r="H35" s="22">
-        <f>G35/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.28616878100000004</v>
       </c>
       <c r="I35" s="23" t="s">
@@ -2148,7 +2193,7 @@
         <v>950</v>
       </c>
       <c r="H36" s="22">
-        <f>G36/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.30240305000000001</v>
       </c>
       <c r="I36" s="23" t="s">
@@ -2178,7 +2223,7 @@
         <v>1100</v>
       </c>
       <c r="H37" s="22">
-        <f>G37/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.35015090000000004</v>
       </c>
       <c r="I37" s="23" t="s">
@@ -2208,7 +2253,7 @@
         <v>57</v>
       </c>
       <c r="H38" s="35">
-        <f>G38/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I38" s="36" t="s">
@@ -2238,7 +2283,7 @@
         <v>72</v>
       </c>
       <c r="H39" s="35">
-        <f>G39/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>2.2918967999999998E-2</v>
       </c>
       <c r="I39" s="36" t="s">
@@ -2268,7 +2313,7 @@
         <v>255</v>
       </c>
       <c r="H40" s="35">
-        <f>G40/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>8.1171345000000006E-2</v>
       </c>
       <c r="I40" s="36" t="s">
@@ -2298,7 +2343,7 @@
         <v>424</v>
       </c>
       <c r="H41" s="35">
-        <f>G41/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.13496725600000001</v>
       </c>
       <c r="I41" s="36" t="s">
@@ -2328,7 +2373,7 @@
         <v>483</v>
       </c>
       <c r="H42" s="35">
-        <f>G42/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.15374807700000001</v>
       </c>
       <c r="I42" s="36" t="s">
@@ -2358,7 +2403,7 @@
         <v>536</v>
       </c>
       <c r="H43" s="35">
-        <f>G43/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.17061898400000003</v>
       </c>
       <c r="I43" s="36" t="s">
@@ -2388,7 +2433,7 @@
         <v>46</v>
       </c>
       <c r="H44" s="10">
-        <f>G44/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>1.4642674000000001E-2</v>
       </c>
       <c r="I44" s="11" t="s">
@@ -2418,7 +2463,7 @@
         <v>326</v>
       </c>
       <c r="H45" s="10">
-        <f>G45/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.10377199400000001</v>
       </c>
       <c r="I45" s="11" t="s">
@@ -2448,7 +2493,7 @@
         <v>464</v>
       </c>
       <c r="H46" s="10">
-        <f>G46/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.14770001600000002</v>
       </c>
       <c r="I46" s="11" t="s">
@@ -2478,7 +2523,7 @@
         <v>578</v>
       </c>
       <c r="H47" s="10">
-        <f>G47/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.18398838200000001</v>
       </c>
       <c r="I47" s="11" t="s">
@@ -2508,7 +2553,7 @@
         <v>635</v>
       </c>
       <c r="H48" s="10">
-        <f>G48/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.20213256500000001</v>
       </c>
       <c r="I48" s="11" t="s">
@@ -2538,7 +2583,7 @@
         <v>678</v>
       </c>
       <c r="H49" s="10">
-        <f>G49/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.21582028200000003</v>
       </c>
       <c r="I49" s="11" t="s">
@@ -2568,7 +2613,7 @@
         <v>54</v>
       </c>
       <c r="H50" s="16">
-        <f>G50/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>1.7189226000000002E-2</v>
       </c>
       <c r="I50" s="17" t="s">
@@ -2598,7 +2643,7 @@
         <v>85</v>
       </c>
       <c r="H51" s="16">
-        <f>G51/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>2.7057115000000003E-2</v>
       </c>
       <c r="I51" s="17" t="s">
@@ -2628,7 +2673,7 @@
         <v>468</v>
       </c>
       <c r="H52" s="16">
-        <f>G52/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.14897329200000001</v>
       </c>
       <c r="I52" s="17" t="s">
@@ -2658,7 +2703,7 @@
         <v>636</v>
       </c>
       <c r="H53" s="16">
-        <f>G53/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.20245088400000003</v>
       </c>
       <c r="I53" s="17" t="s">
@@ -2688,7 +2733,7 @@
         <v>685</v>
       </c>
       <c r="H54" s="16">
-        <f>G54/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.21804851500000003</v>
       </c>
       <c r="I54" s="17" t="s">
@@ -2718,7 +2763,7 @@
         <v>708</v>
       </c>
       <c r="H55" s="16">
-        <f>G55/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.22536985200000001</v>
       </c>
       <c r="I55" s="17" t="s">
@@ -2748,7 +2793,7 @@
         <v>59</v>
       </c>
       <c r="H56" s="10">
-        <f>G56/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>1.8780821E-2</v>
       </c>
       <c r="I56" s="11" t="s">
@@ -2778,7 +2823,7 @@
         <v>106</v>
       </c>
       <c r="H57" s="10">
-        <f>G57/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>3.3741814000000002E-2</v>
       </c>
       <c r="I57" s="11" t="s">
@@ -2808,7 +2853,7 @@
         <v>305</v>
       </c>
       <c r="H58" s="10">
-        <f>G58/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>9.7087295000000004E-2</v>
       </c>
       <c r="I58" s="11" t="s">
@@ -2838,7 +2883,7 @@
         <v>425</v>
       </c>
       <c r="H59" s="10">
-        <f>G59/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.13528557499999999</v>
       </c>
       <c r="I59" s="11" t="s">
@@ -2868,7 +2913,7 @@
         <v>466</v>
       </c>
       <c r="H60" s="10">
-        <f>G60/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.14833665400000001</v>
       </c>
       <c r="I60" s="11" t="s">
@@ -2898,7 +2943,7 @@
         <v>486</v>
       </c>
       <c r="H61" s="10">
-        <f>G61/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.15470303400000002</v>
       </c>
       <c r="I61" s="11" t="s">
@@ -2928,7 +2973,7 @@
         <v>-23</v>
       </c>
       <c r="H62" s="16">
-        <f>G62/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>-7.3213370000000007E-3</v>
       </c>
       <c r="I62" s="17" t="s">
@@ -2958,7 +3003,7 @@
         <v>83</v>
       </c>
       <c r="H63" s="16">
-        <f>G63/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>2.6420477000000001E-2</v>
       </c>
       <c r="I63" s="17" t="s">
@@ -2988,7 +3033,7 @@
         <v>342</v>
       </c>
       <c r="H64" s="16">
-        <f>G64/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.10886509800000002</v>
       </c>
       <c r="I64" s="17" t="s">
@@ -3018,7 +3063,7 @@
         <v>546</v>
       </c>
       <c r="H65" s="16">
-        <f>G65/1000*0.318319</f>
+        <f t="shared" si="1"/>
         <v>0.17380217400000003</v>
       </c>
       <c r="I65" s="17" t="s">
@@ -3048,7 +3093,7 @@
         <v>657</v>
       </c>
       <c r="H66" s="16">
-        <f>G66/1000*0.318319</f>
+        <f t="shared" ref="H66:H97" si="2">G66/1000*0.318319</f>
         <v>0.20913558300000001</v>
       </c>
       <c r="I66" s="17" t="s">
@@ -3078,7 +3123,7 @@
         <v>763</v>
       </c>
       <c r="H67" s="16">
-        <f>G67/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.24287739700000002</v>
       </c>
       <c r="I67" s="17" t="s">
@@ -3108,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="H68" s="22">
-        <f>G68/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>2.5465520000000001E-3</v>
       </c>
       <c r="I68" s="23" t="s">
@@ -3138,7 +3183,7 @@
         <v>15</v>
       </c>
       <c r="H69" s="22">
-        <f>G69/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>4.7747850000000001E-3</v>
       </c>
       <c r="I69" s="23" t="s">
@@ -3168,7 +3213,7 @@
         <v>88</v>
       </c>
       <c r="H70" s="22">
-        <f>G70/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>2.8012071999999999E-2</v>
       </c>
       <c r="I70" s="23" t="s">
@@ -3198,7 +3243,7 @@
         <v>166</v>
       </c>
       <c r="H71" s="22">
-        <f>G71/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>5.2840954000000002E-2</v>
       </c>
       <c r="I71" s="23" t="s">
@@ -3228,7 +3273,7 @@
         <v>258</v>
       </c>
       <c r="H72" s="22">
-        <f>G72/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>8.2126302000000012E-2</v>
       </c>
       <c r="I72" s="23" t="s">
@@ -3258,7 +3303,7 @@
         <v>367</v>
       </c>
       <c r="H73" s="22">
-        <f>G73/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.116823073</v>
       </c>
       <c r="I73" s="23" t="s">
@@ -3288,7 +3333,7 @@
         <v>456</v>
       </c>
       <c r="H74" s="22">
-        <f>G74/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.14515346400000001</v>
       </c>
       <c r="I74" s="23" t="s">
@@ -3318,7 +3363,7 @@
         <v>467</v>
       </c>
       <c r="H75" s="22">
-        <f>G75/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.14865497300000002</v>
       </c>
       <c r="I75" s="23" t="s">
@@ -3348,7 +3393,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="10">
-        <f>G76/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>7.9579750000000008E-3</v>
       </c>
       <c r="I76" s="11" t="s">
@@ -3378,7 +3423,7 @@
         <v>35</v>
       </c>
       <c r="H77" s="10">
-        <f>G77/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>1.1141165000000001E-2</v>
       </c>
       <c r="I77" s="11" t="s">
@@ -3408,7 +3453,7 @@
         <v>84</v>
       </c>
       <c r="H78" s="10">
-        <f>G78/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>2.6738796000000002E-2</v>
       </c>
       <c r="I78" s="11" t="s">
@@ -3438,7 +3483,7 @@
         <v>165</v>
       </c>
       <c r="H79" s="10">
-        <f>G79/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>5.2522635000000005E-2</v>
       </c>
       <c r="I79" s="11" t="s">
@@ -3468,7 +3513,7 @@
         <v>254</v>
       </c>
       <c r="H80" s="10">
-        <f>G80/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>8.0853026000000008E-2</v>
       </c>
       <c r="I80" s="11" t="s">
@@ -3498,7 +3543,7 @@
         <v>354</v>
       </c>
       <c r="H81" s="10">
-        <f>G81/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.112684926</v>
       </c>
       <c r="I81" s="11" t="s">
@@ -3528,7 +3573,7 @@
         <v>464</v>
       </c>
       <c r="H82" s="10">
-        <f>G82/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.14770001600000002</v>
       </c>
       <c r="I82" s="11" t="s">
@@ -3558,7 +3603,7 @@
         <v>536</v>
       </c>
       <c r="H83" s="10">
-        <f>G83/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.17061898400000003</v>
       </c>
       <c r="I83" s="11" t="s">
@@ -3588,7 +3633,7 @@
         <v>10</v>
       </c>
       <c r="H84" s="28">
-        <f>G84/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>3.1831900000000002E-3</v>
       </c>
       <c r="I84" s="29" t="s">
@@ -3618,7 +3663,7 @@
         <v>23</v>
       </c>
       <c r="H85" s="28">
-        <f>G85/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>7.3213370000000007E-3</v>
       </c>
       <c r="I85" s="29" t="s">
@@ -3648,7 +3693,7 @@
         <v>264</v>
       </c>
       <c r="H86" s="28">
-        <f>G86/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>8.4036216000000011E-2</v>
       </c>
       <c r="I86" s="29" t="s">
@@ -3678,7 +3723,7 @@
         <v>576</v>
       </c>
       <c r="H87" s="28">
-        <f>G87/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.18335174399999998</v>
       </c>
       <c r="I87" s="29" t="s">
@@ -3708,7 +3753,7 @@
         <v>719</v>
       </c>
       <c r="H88" s="28">
-        <f>G88/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.228871361</v>
       </c>
       <c r="I88" s="29" t="s">
@@ -3738,7 +3783,7 @@
         <v>849</v>
       </c>
       <c r="H89" s="28">
-        <f>G89/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.27025283100000003</v>
       </c>
       <c r="I89" s="29" t="s">
@@ -3768,7 +3813,7 @@
         <v>980</v>
       </c>
       <c r="H90" s="28">
-        <f>G90/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.31195262000000001</v>
       </c>
       <c r="I90" s="29" t="s">
@@ -3798,7 +3843,7 @@
         <v>1017</v>
       </c>
       <c r="H91" s="28">
-        <f>G91/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.32373042299999999</v>
       </c>
       <c r="I91" s="29" t="s">
@@ -3828,7 +3873,7 @@
         <v>81</v>
       </c>
       <c r="H92" s="35">
-        <f>G92/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>2.5783839000000003E-2</v>
       </c>
       <c r="I92" s="36" t="s">
@@ -3858,7 +3903,7 @@
         <v>342</v>
       </c>
       <c r="H93" s="35">
-        <f>G93/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.10886509800000002</v>
       </c>
       <c r="I93" s="36" t="s">
@@ -3888,7 +3933,7 @@
         <v>452</v>
       </c>
       <c r="H94" s="35">
-        <f>G94/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.14388018800000002</v>
       </c>
       <c r="I94" s="36" t="s">
@@ -3918,7 +3963,7 @@
         <v>539</v>
       </c>
       <c r="H95" s="35">
-        <f>G95/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.17157394100000001</v>
       </c>
       <c r="I95" s="36" t="s">
@@ -3948,7 +3993,7 @@
         <v>714</v>
       </c>
       <c r="H96" s="35">
-        <f>G96/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.22727976599999999</v>
       </c>
       <c r="I96" s="36" t="s">
@@ -3978,7 +4023,7 @@
         <v>966</v>
       </c>
       <c r="H97" s="35">
-        <f>G97/1000*0.318319</f>
+        <f t="shared" si="2"/>
         <v>0.30749615400000002</v>
       </c>
       <c r="I97" s="36" t="s">
@@ -4008,7 +4053,7 @@
         <v>1514</v>
       </c>
       <c r="H98" s="35">
-        <f>G98/1000*0.318319</f>
+        <f t="shared" ref="H98:H129" si="3">G98/1000*0.318319</f>
         <v>0.48193496600000002</v>
       </c>
       <c r="I98" s="36" t="s">
@@ -4038,7 +4083,7 @@
         <v>1777</v>
       </c>
       <c r="H99" s="35">
-        <f>G99/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.56565286299999995</v>
       </c>
       <c r="I99" s="36" t="s">
@@ -4068,7 +4113,7 @@
         <v>27</v>
       </c>
       <c r="H100" s="10">
-        <f>G100/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>8.5946130000000009E-3</v>
       </c>
       <c r="I100" s="11" t="s">
@@ -4098,7 +4143,7 @@
         <v>109</v>
       </c>
       <c r="H101" s="10">
-        <f>G101/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>3.4696771000000001E-2</v>
       </c>
       <c r="I101" s="11" t="s">
@@ -4128,7 +4173,7 @@
         <v>157</v>
       </c>
       <c r="H102" s="10">
-        <f>G102/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>4.9976083000000004E-2</v>
       </c>
       <c r="I102" s="11" t="s">
@@ -4158,7 +4203,7 @@
         <v>355</v>
       </c>
       <c r="H103" s="10">
-        <f>G103/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.113003245</v>
       </c>
       <c r="I103" s="11" t="s">
@@ -4188,7 +4233,7 @@
         <v>515</v>
       </c>
       <c r="H104" s="10">
-        <f>G104/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.16393428500000001</v>
       </c>
       <c r="I104" s="11" t="s">
@@ -4218,7 +4263,7 @@
         <v>659</v>
       </c>
       <c r="H105" s="10">
-        <f>G105/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.20977222100000001</v>
       </c>
       <c r="I105" s="11" t="s">
@@ -4248,7 +4293,7 @@
         <v>858</v>
       </c>
       <c r="H106" s="10">
-        <f>G106/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.27311770200000002</v>
       </c>
       <c r="I106" s="11" t="s">
@@ -4278,7 +4323,7 @@
         <v>957</v>
       </c>
       <c r="H107" s="10">
-        <f>G107/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.30463128300000003</v>
       </c>
       <c r="I107" s="11" t="s">
@@ -4308,7 +4353,7 @@
         <v>185</v>
       </c>
       <c r="H108" s="35">
-        <f>G108/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>5.8889015000000003E-2</v>
       </c>
       <c r="I108" s="36" t="s">
@@ -4338,7 +4383,7 @@
         <v>318</v>
       </c>
       <c r="H109" s="35">
-        <f>G109/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.10122544200000001</v>
       </c>
       <c r="I109" s="36" t="s">
@@ -4368,7 +4413,7 @@
         <v>447</v>
       </c>
       <c r="H110" s="35">
-        <f>G110/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.14228859300000002</v>
       </c>
       <c r="I110" s="36" t="s">
@@ -4398,7 +4443,7 @@
         <v>609</v>
       </c>
       <c r="H111" s="35">
-        <f>G111/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.193856271</v>
       </c>
       <c r="I111" s="36" t="s">
@@ -4428,7 +4473,7 @@
         <v>979</v>
       </c>
       <c r="H112" s="35">
-        <f>G112/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.311634301</v>
       </c>
       <c r="I112" s="36" t="s">
@@ -4458,7 +4503,7 @@
         <v>1337</v>
       </c>
       <c r="H113" s="35">
-        <f>G113/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.42559250300000001</v>
       </c>
       <c r="I113" s="36" t="s">
@@ -4488,7 +4533,7 @@
         <v>1741</v>
       </c>
       <c r="H114" s="35">
-        <f>G114/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.5541933790000001</v>
       </c>
       <c r="I114" s="36" t="s">
@@ -4518,7 +4563,7 @@
         <v>1988</v>
       </c>
       <c r="H115" s="35">
-        <f>G115/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.63281817200000001</v>
       </c>
       <c r="I115" s="36" t="s">
@@ -4548,7 +4593,7 @@
         <v>148</v>
       </c>
       <c r="H116" s="16">
-        <f>G116/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>4.7111212E-2</v>
       </c>
       <c r="I116" s="17" t="s">
@@ -4578,7 +4623,7 @@
         <v>179</v>
       </c>
       <c r="H117" s="16">
-        <f>G117/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>5.6979101000000004E-2</v>
       </c>
       <c r="I117" s="17" t="s">
@@ -4608,7 +4653,7 @@
         <v>266</v>
       </c>
       <c r="H118" s="16">
-        <f>G118/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>8.4672854000000006E-2</v>
       </c>
       <c r="I118" s="17" t="s">
@@ -4638,7 +4683,7 @@
         <v>396</v>
       </c>
       <c r="H119" s="16">
-        <f>G119/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.12605432400000002</v>
       </c>
       <c r="I119" s="17" t="s">
@@ -4668,7 +4713,7 @@
         <v>497</v>
       </c>
       <c r="H120" s="16">
-        <f>G120/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.158204543</v>
       </c>
       <c r="I120" s="17" t="s">
@@ -4698,7 +4743,7 @@
         <v>606</v>
       </c>
       <c r="H121" s="16">
-        <f>G121/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.19290131400000002</v>
       </c>
       <c r="I121" s="17" t="s">
@@ -4728,7 +4773,7 @@
         <v>741</v>
       </c>
       <c r="H122" s="16">
-        <f>G122/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.23587437900000002</v>
       </c>
       <c r="I122" s="17" t="s">
@@ -4758,7 +4803,7 @@
         <v>839</v>
       </c>
       <c r="H123" s="16">
-        <f>G123/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.26706964100000002</v>
       </c>
       <c r="I123" s="17" t="s">
@@ -4788,7 +4833,7 @@
         <v>125</v>
       </c>
       <c r="H124" s="10">
-        <f>G124/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>3.9789875000000002E-2</v>
       </c>
       <c r="I124" s="11" t="s">
@@ -4818,7 +4863,7 @@
         <v>283</v>
       </c>
       <c r="H125" s="10">
-        <f>G125/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>9.008427699999999E-2</v>
       </c>
       <c r="I125" s="11" t="s">
@@ -4848,7 +4893,7 @@
         <v>386</v>
       </c>
       <c r="H126" s="10">
-        <f>G126/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.12287113400000001</v>
       </c>
       <c r="I126" s="11" t="s">
@@ -4878,7 +4923,7 @@
         <v>487</v>
       </c>
       <c r="H127" s="10">
-        <f>G127/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.155021353</v>
       </c>
       <c r="I127" s="11" t="s">
@@ -4908,7 +4953,7 @@
         <v>582</v>
       </c>
       <c r="H128" s="10">
-        <f>G128/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.185261658</v>
       </c>
       <c r="I128" s="11" t="s">
@@ -4938,7 +4983,7 @@
         <v>655</v>
       </c>
       <c r="H129" s="10">
-        <f>G129/1000*0.318319</f>
+        <f t="shared" si="3"/>
         <v>0.20849894500000002</v>
       </c>
       <c r="I129" s="11" t="s">
@@ -4968,7 +5013,7 @@
         <v>744</v>
       </c>
       <c r="H130" s="10">
-        <f>G130/1000*0.318319</f>
+        <f t="shared" ref="H130:H187" si="4">G130/1000*0.318319</f>
         <v>0.236829336</v>
       </c>
       <c r="I130" s="11" t="s">
@@ -4998,7 +5043,7 @@
         <v>802</v>
       </c>
       <c r="H131" s="10">
-        <f>G131/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.25529183800000005</v>
       </c>
       <c r="I131" s="11" t="s">
@@ -5028,7 +5073,7 @@
         <v>15</v>
       </c>
       <c r="H132" s="22">
-        <f>G132/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>4.7747850000000001E-3</v>
       </c>
       <c r="I132" s="23" t="s">
@@ -5058,7 +5103,7 @@
         <v>57</v>
       </c>
       <c r="H133" s="22">
-        <f>G133/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I133" s="23" t="s">
@@ -5088,7 +5133,7 @@
         <v>178</v>
       </c>
       <c r="H134" s="22">
-        <f>G134/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>5.6660782E-2</v>
       </c>
       <c r="I134" s="23" t="s">
@@ -5118,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="H135" s="22">
-        <f>G135/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>8.3081259000000005E-2</v>
       </c>
       <c r="I135" s="23" t="s">
@@ -5148,7 +5193,7 @@
         <v>351</v>
       </c>
       <c r="H136" s="22">
-        <f>G136/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.111729969</v>
       </c>
       <c r="I136" s="23" t="s">
@@ -5178,7 +5223,7 @@
         <v>457</v>
       </c>
       <c r="H137" s="22">
-        <f>G137/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.14547178300000002</v>
       </c>
       <c r="I137" s="23" t="s">
@@ -5208,7 +5253,7 @@
         <v>608</v>
       </c>
       <c r="H138" s="22">
-        <f>G138/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.19353795200000001</v>
       </c>
       <c r="I138" s="23" t="s">
@@ -5238,7 +5283,7 @@
         <v>740</v>
       </c>
       <c r="H139" s="22">
-        <f>G139/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.23555606000000001</v>
       </c>
       <c r="I139" s="23" t="s">
@@ -5268,7 +5313,7 @@
         <v>57</v>
       </c>
       <c r="H140" s="35">
-        <f>G140/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I140" s="36" t="s">
@@ -5298,7 +5343,7 @@
         <v>88</v>
       </c>
       <c r="H141" s="35">
-        <f>G141/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>2.8012071999999999E-2</v>
       </c>
       <c r="I141" s="36" t="s">
@@ -5328,7 +5373,7 @@
         <v>134</v>
       </c>
       <c r="H142" s="35">
-        <f>G142/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>4.2654746000000007E-2</v>
       </c>
       <c r="I142" s="36" t="s">
@@ -5358,7 +5403,7 @@
         <v>225</v>
       </c>
       <c r="H143" s="35">
-        <f>G143/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>7.1621775000000013E-2</v>
       </c>
       <c r="I143" s="36" t="s">
@@ -5388,7 +5433,7 @@
         <v>319</v>
       </c>
       <c r="H144" s="35">
-        <f>G144/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.10154376100000001</v>
       </c>
       <c r="I144" s="36" t="s">
@@ -5418,7 +5463,7 @@
         <v>446</v>
       </c>
       <c r="H145" s="35">
-        <f>G145/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.14197027400000001</v>
       </c>
       <c r="I145" s="36" t="s">
@@ -5448,7 +5493,7 @@
         <v>648</v>
       </c>
       <c r="H146" s="35">
-        <f>G146/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.20627071200000002</v>
       </c>
       <c r="I146" s="36" t="s">
@@ -5478,7 +5523,7 @@
         <v>708</v>
       </c>
       <c r="H147" s="35">
-        <f>G147/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.22536985200000001</v>
       </c>
       <c r="I147" s="36" t="s">
@@ -5508,7 +5553,7 @@
         <v>-26</v>
       </c>
       <c r="H148" s="16">
-        <f>G148/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>-8.276294E-3</v>
       </c>
       <c r="I148" s="17" t="s">
@@ -5538,7 +5583,7 @@
         <v>10</v>
       </c>
       <c r="H149" s="16">
-        <f>G149/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>3.1831900000000002E-3</v>
       </c>
       <c r="I149" s="17" t="s">
@@ -5568,7 +5613,7 @@
         <v>69</v>
       </c>
       <c r="H150" s="16">
-        <f>G150/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>2.1964011000000002E-2</v>
       </c>
       <c r="I150" s="17" t="s">
@@ -5598,7 +5643,7 @@
         <v>236</v>
       </c>
       <c r="H151" s="16">
-        <f>G151/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>7.5123283999999999E-2</v>
       </c>
       <c r="I151" s="17" t="s">
@@ -5628,7 +5673,7 @@
         <v>394</v>
       </c>
       <c r="H152" s="16">
-        <f>G152/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.125417686</v>
       </c>
       <c r="I152" s="17" t="s">
@@ -5658,7 +5703,7 @@
         <v>645</v>
       </c>
       <c r="H153" s="16">
-        <f>G153/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.20531575500000002</v>
       </c>
       <c r="I153" s="17" t="s">
@@ -5688,7 +5733,7 @@
         <v>838</v>
       </c>
       <c r="H154" s="16">
-        <f>G154/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.26675132200000001</v>
       </c>
       <c r="I154" s="17" t="s">
@@ -5718,10 +5763,970 @@
         <v>996</v>
       </c>
       <c r="H155" s="16">
-        <f>G155/1000*0.318319</f>
+        <f t="shared" si="4"/>
         <v>0.31704572400000003</v>
       </c>
       <c r="I155" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="6">
+        <v>60</v>
+      </c>
+      <c r="E156" s="8">
+        <v>0</v>
+      </c>
+      <c r="F156" s="9">
+        <v>0</v>
+      </c>
+      <c r="G156" s="8">
+        <v>68</v>
+      </c>
+      <c r="H156" s="10">
+        <f t="shared" si="4"/>
+        <v>2.1645692000000001E-2</v>
+      </c>
+      <c r="I156" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="6">
+        <v>60</v>
+      </c>
+      <c r="E157" s="8">
+        <v>1</v>
+      </c>
+      <c r="F157" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="G157" s="8">
+        <v>88</v>
+      </c>
+      <c r="H157" s="10">
+        <f t="shared" si="4"/>
+        <v>2.8012071999999999E-2</v>
+      </c>
+      <c r="I157" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A158" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="6">
+        <v>60</v>
+      </c>
+      <c r="E158" s="8">
+        <v>2</v>
+      </c>
+      <c r="F158" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="G158" s="8">
+        <v>155</v>
+      </c>
+      <c r="H158" s="10">
+        <f t="shared" si="4"/>
+        <v>4.9339445000000003E-2</v>
+      </c>
+      <c r="I158" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A159" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="6">
+        <v>60</v>
+      </c>
+      <c r="E159" s="8">
+        <v>3</v>
+      </c>
+      <c r="F159" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="G159" s="8">
+        <v>259</v>
+      </c>
+      <c r="H159" s="10">
+        <f t="shared" si="4"/>
+        <v>8.244462100000001E-2</v>
+      </c>
+      <c r="I159" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="6">
+        <v>60</v>
+      </c>
+      <c r="E160" s="8">
+        <v>4</v>
+      </c>
+      <c r="F160" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G160" s="8">
+        <v>384</v>
+      </c>
+      <c r="H160" s="10">
+        <f t="shared" si="4"/>
+        <v>0.12223449600000001</v>
+      </c>
+      <c r="I160" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="6">
+        <v>60</v>
+      </c>
+      <c r="E161" s="8">
+        <v>5</v>
+      </c>
+      <c r="F161" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="G161" s="8">
+        <v>505</v>
+      </c>
+      <c r="H161" s="10">
+        <f t="shared" si="4"/>
+        <v>0.16075109500000001</v>
+      </c>
+      <c r="I161" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A162" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="6">
+        <v>60</v>
+      </c>
+      <c r="E162" s="8">
+        <v>7</v>
+      </c>
+      <c r="F162" s="9">
+        <v>0.87</v>
+      </c>
+      <c r="G162" s="8">
+        <v>708</v>
+      </c>
+      <c r="H162" s="10">
+        <f t="shared" si="4"/>
+        <v>0.22536985200000001</v>
+      </c>
+      <c r="I162" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A163" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="6">
+        <v>60</v>
+      </c>
+      <c r="E163" s="8">
+        <v>10</v>
+      </c>
+      <c r="F163" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="G163" s="8">
+        <v>886</v>
+      </c>
+      <c r="H163" s="10">
+        <f t="shared" si="4"/>
+        <v>0.282030634</v>
+      </c>
+      <c r="I163" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A164" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B164" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C164" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="31">
+        <v>60</v>
+      </c>
+      <c r="E164" s="33">
+        <v>0</v>
+      </c>
+      <c r="F164" s="34">
+        <v>0</v>
+      </c>
+      <c r="G164" s="33">
+        <v>-33</v>
+      </c>
+      <c r="H164" s="35">
+        <f t="shared" si="4"/>
+        <v>-1.0504527000000001E-2</v>
+      </c>
+      <c r="I164" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A165" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B165" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C165" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="31">
+        <v>60</v>
+      </c>
+      <c r="E165" s="33">
+        <v>1</v>
+      </c>
+      <c r="F165" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="G165" s="33">
+        <v>-2</v>
+      </c>
+      <c r="H165" s="35">
+        <f t="shared" si="4"/>
+        <v>-6.3663800000000003E-4</v>
+      </c>
+      <c r="I165" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A166" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B166" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C166" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="31">
+        <v>60</v>
+      </c>
+      <c r="E166" s="33">
+        <v>2</v>
+      </c>
+      <c r="F166" s="34">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G166" s="33">
+        <v>26</v>
+      </c>
+      <c r="H166" s="35">
+        <f t="shared" si="4"/>
+        <v>8.276294E-3</v>
+      </c>
+      <c r="I166" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A167" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B167" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C167" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="31">
+        <v>60</v>
+      </c>
+      <c r="E167" s="33">
+        <v>3</v>
+      </c>
+      <c r="F167" s="34">
+        <v>0.43</v>
+      </c>
+      <c r="G167" s="33">
+        <v>86</v>
+      </c>
+      <c r="H167" s="35">
+        <f t="shared" si="4"/>
+        <v>2.7375434000000001E-2</v>
+      </c>
+      <c r="I167" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A168" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C168" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="31">
+        <v>60</v>
+      </c>
+      <c r="E168" s="33">
+        <v>4</v>
+      </c>
+      <c r="F168" s="34">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G168" s="33">
+        <v>188</v>
+      </c>
+      <c r="H168" s="35">
+        <f t="shared" si="4"/>
+        <v>5.9843972000000002E-2</v>
+      </c>
+      <c r="I168" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A169" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B169" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C169" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D169" s="31">
+        <v>60</v>
+      </c>
+      <c r="E169" s="33">
+        <v>5</v>
+      </c>
+      <c r="F169" s="34">
+        <v>0.69</v>
+      </c>
+      <c r="G169" s="33">
+        <v>248</v>
+      </c>
+      <c r="H169" s="35">
+        <f t="shared" si="4"/>
+        <v>7.894311200000001E-2</v>
+      </c>
+      <c r="I169" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A170" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B170" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C170" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D170" s="31">
+        <v>60</v>
+      </c>
+      <c r="E170" s="33">
+        <v>7</v>
+      </c>
+      <c r="F170" s="34">
+        <v>0.85</v>
+      </c>
+      <c r="G170" s="33">
+        <v>378</v>
+      </c>
+      <c r="H170" s="35">
+        <f t="shared" si="4"/>
+        <v>0.12032458200000001</v>
+      </c>
+      <c r="I170" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A171" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B171" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C171" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D171" s="31">
+        <v>60</v>
+      </c>
+      <c r="E171" s="33">
+        <v>10</v>
+      </c>
+      <c r="F171" s="34">
+        <v>0.96</v>
+      </c>
+      <c r="G171" s="33">
+        <v>458</v>
+      </c>
+      <c r="H171" s="35">
+        <f t="shared" si="4"/>
+        <v>0.145790102</v>
+      </c>
+      <c r="I171" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A172" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B172" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C172" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="18">
+        <v>60</v>
+      </c>
+      <c r="E172" s="20">
+        <v>0</v>
+      </c>
+      <c r="F172" s="21">
+        <v>0</v>
+      </c>
+      <c r="G172" s="20">
+        <v>-44</v>
+      </c>
+      <c r="H172" s="22">
+        <f t="shared" si="4"/>
+        <v>-1.4006035999999999E-2</v>
+      </c>
+      <c r="I172" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A173" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C173" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" s="18">
+        <v>60</v>
+      </c>
+      <c r="E173" s="20">
+        <v>1</v>
+      </c>
+      <c r="F173" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="G173" s="20">
+        <v>-32</v>
+      </c>
+      <c r="H173" s="22">
+        <f t="shared" si="4"/>
+        <v>-1.0186208E-2</v>
+      </c>
+      <c r="I173" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A174" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B174" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C174" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="18">
+        <v>60</v>
+      </c>
+      <c r="E174" s="20">
+        <v>2</v>
+      </c>
+      <c r="F174" s="21">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G174" s="20">
+        <v>56</v>
+      </c>
+      <c r="H174" s="22">
+        <f t="shared" si="4"/>
+        <v>1.7825864E-2</v>
+      </c>
+      <c r="I174" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A175" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B175" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C175" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="18">
+        <v>60</v>
+      </c>
+      <c r="E175" s="20">
+        <v>3</v>
+      </c>
+      <c r="F175" s="21">
+        <v>0.43</v>
+      </c>
+      <c r="G175" s="20">
+        <v>117</v>
+      </c>
+      <c r="H175" s="22">
+        <f t="shared" si="4"/>
+        <v>3.7243323000000002E-2</v>
+      </c>
+      <c r="I175" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A176" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B176" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C176" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="18">
+        <v>60</v>
+      </c>
+      <c r="E176" s="20">
+        <v>4</v>
+      </c>
+      <c r="F176" s="21">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G176" s="20">
+        <v>216</v>
+      </c>
+      <c r="H176" s="22">
+        <f t="shared" si="4"/>
+        <v>6.8756904000000008E-2</v>
+      </c>
+      <c r="I176" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A177" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B177" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C177" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D177" s="18">
+        <v>60</v>
+      </c>
+      <c r="E177" s="20">
+        <v>5</v>
+      </c>
+      <c r="F177" s="21">
+        <v>0.69</v>
+      </c>
+      <c r="G177" s="20">
+        <v>327</v>
+      </c>
+      <c r="H177" s="22">
+        <f t="shared" si="4"/>
+        <v>0.104090313</v>
+      </c>
+      <c r="I177" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A178" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B178" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C178" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D178" s="18">
+        <v>60</v>
+      </c>
+      <c r="E178" s="20">
+        <v>7</v>
+      </c>
+      <c r="F178" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="G178" s="20">
+        <v>447</v>
+      </c>
+      <c r="H178" s="22">
+        <f t="shared" si="4"/>
+        <v>0.14228859300000002</v>
+      </c>
+      <c r="I178" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A179" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B179" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C179" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" s="18">
+        <v>60</v>
+      </c>
+      <c r="E179" s="20">
+        <v>10</v>
+      </c>
+      <c r="F179" s="21">
+        <v>0.96</v>
+      </c>
+      <c r="G179" s="20">
+        <v>609</v>
+      </c>
+      <c r="H179" s="22">
+        <f t="shared" si="4"/>
+        <v>0.193856271</v>
+      </c>
+      <c r="I179" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A180" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="12">
+        <v>60</v>
+      </c>
+      <c r="E180" s="14">
+        <v>0</v>
+      </c>
+      <c r="F180" s="15">
+        <v>0</v>
+      </c>
+      <c r="G180" s="14">
+        <v>-2</v>
+      </c>
+      <c r="H180" s="16">
+        <f t="shared" si="4"/>
+        <v>-6.3663800000000003E-4</v>
+      </c>
+      <c r="I180" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A181" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="12">
+        <v>60</v>
+      </c>
+      <c r="E181" s="14">
+        <v>1</v>
+      </c>
+      <c r="F181" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="G181" s="14">
+        <v>17</v>
+      </c>
+      <c r="H181" s="16">
+        <f t="shared" si="4"/>
+        <v>5.4114230000000003E-3</v>
+      </c>
+      <c r="I181" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A182" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="12">
+        <v>60</v>
+      </c>
+      <c r="E182" s="14">
+        <v>2</v>
+      </c>
+      <c r="F182" s="15">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G182" s="14">
+        <v>86</v>
+      </c>
+      <c r="H182" s="16">
+        <f t="shared" si="4"/>
+        <v>2.7375434000000001E-2</v>
+      </c>
+      <c r="I182" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A183" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C183" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="12">
+        <v>60</v>
+      </c>
+      <c r="E183" s="14">
+        <v>3</v>
+      </c>
+      <c r="F183" s="15">
+        <v>0.43</v>
+      </c>
+      <c r="G183" s="14">
+        <v>216</v>
+      </c>
+      <c r="H183" s="16">
+        <f t="shared" si="4"/>
+        <v>6.8756904000000008E-2</v>
+      </c>
+      <c r="I183" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A184" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="12">
+        <v>60</v>
+      </c>
+      <c r="E184" s="14">
+        <v>4</v>
+      </c>
+      <c r="F184" s="15">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G184" s="14">
+        <v>337</v>
+      </c>
+      <c r="H184" s="16">
+        <f t="shared" si="4"/>
+        <v>0.10727350300000002</v>
+      </c>
+      <c r="I184" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A185" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C185" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="12">
+        <v>60</v>
+      </c>
+      <c r="E185" s="14">
+        <v>5</v>
+      </c>
+      <c r="F185" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="G185" s="14">
+        <v>488</v>
+      </c>
+      <c r="H185" s="16">
+        <f t="shared" si="4"/>
+        <v>0.15533967200000001</v>
+      </c>
+      <c r="I185" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A186" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="12">
+        <v>60</v>
+      </c>
+      <c r="E186" s="14">
+        <v>7</v>
+      </c>
+      <c r="F186" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="G186" s="14">
+        <v>667</v>
+      </c>
+      <c r="H186" s="16">
+        <f t="shared" si="4"/>
+        <v>0.21231877300000002</v>
+      </c>
+      <c r="I186" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A187" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="12">
+        <v>60</v>
+      </c>
+      <c r="E187" s="14">
+        <v>10</v>
+      </c>
+      <c r="F187" s="15">
+        <v>0.97</v>
+      </c>
+      <c r="G187" s="14">
+        <v>829</v>
+      </c>
+      <c r="H187" s="16">
+        <f t="shared" si="4"/>
+        <v>0.26388645100000002</v>
+      </c>
+      <c r="I187" s="17" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5868,20 +6873,36 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
+      <c r="A16" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
+      <c r="A17" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
+      <c r="A18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="37"/>

--- a/自研流变仪材料测试数据.xlsx
+++ b/自研流变仪材料测试数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Desktop\博士\huawei\交付流变仪\自研流变仪测试数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yxin\Desktop\0523\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04038A5E-AD2D-450C-B8C8-920448B6E696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233B88BF-FD17-469D-ACC7-607BE796B370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,30 +18,20 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$67</definedName>
     <definedName name="_xlnm.Data_Form" localSheetId="0" hidden="1">Sheet1!$A$1:$I$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$67</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="137">
   <si>
     <t>平行杆</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -373,6 +363,154 @@
   </si>
   <si>
     <t>0520</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-XD05-STBC-TYY55-91.5-0.4 6.6 3</t>
+  </si>
+  <si>
+    <t>DKN10000-XD05-STBC-TYY55-91.5-0.4 6.6 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0521</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c41</t>
+  </si>
+  <si>
+    <t>c42</t>
+  </si>
+  <si>
+    <t>c43</t>
+  </si>
+  <si>
+    <t>c44</t>
+  </si>
+  <si>
+    <t>c45</t>
+  </si>
+  <si>
+    <t>DKN10000-QX08-STBC-TYY55-91.5-0.4 6.6  3</t>
+  </si>
+  <si>
+    <t>c41</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN50-QZ05-STBC-TYY55-91.9-1.17 6.87 1.96</t>
+  </si>
+  <si>
+    <t>c42</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-XD05-STBC-TYY55-92.5-0.4 6.6 3</t>
+  </si>
+  <si>
+    <t>c43</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ05-STBC-TYY55-91.5-1 8 1</t>
+  </si>
+  <si>
+    <t>c44</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0522</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c45</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ08-STBC-TYY55-92.5-0.4 6.6 3</t>
+  </si>
+  <si>
+    <t>DKN10000-QZ08-STBC-TYY55-92.5-0.4 6.6 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN50-QZ05-STBC-YAFC-91.9-1.17 6.87 1.96</t>
+  </si>
+  <si>
+    <t>c46</t>
+  </si>
+  <si>
+    <t>c46</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c47</t>
+  </si>
+  <si>
+    <t>c48</t>
+  </si>
+  <si>
+    <t>c49</t>
+  </si>
+  <si>
+    <t>c50</t>
+  </si>
+  <si>
+    <t>c47</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ05-STBC-TYY55-90.5-1 8 1</t>
+  </si>
+  <si>
+    <t>DKN10000-QZ05-STBC-TYY55-91.5-1.5 6.5 2</t>
+  </si>
+  <si>
+    <t>c48</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ05-STBC-TYY55-92.5-1.5 6.5 2</t>
+  </si>
+  <si>
+    <t>c49</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-XD05-STBC-XD30-90-0.4 8.6 1</t>
+  </si>
+  <si>
+    <t>c50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ08-STBC-TYY55-92-0.4 6.6 3</t>
+  </si>
+  <si>
+    <t>c51</t>
+  </si>
+  <si>
+    <t>c51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c52</t>
+  </si>
+  <si>
+    <t>0523</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c52</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN10000-QZ08-STBC-TYY55-90-0.4 8.6 1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -384,7 +522,7 @@
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +549,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -482,7 +629,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -556,6 +703,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - 着色 1" xfId="2" builtinId="30"/>
@@ -1110,18 +1287,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I187"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I306"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="39.875" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="1" max="1" width="39.88671875" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" customWidth="1"/>
     <col min="6" max="6" width="9" style="3"/>
-    <col min="7" max="7" width="11.625" customWidth="1"/>
-    <col min="8" max="8" width="14.75" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="5" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1150,7 +1328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -1180,7 +1358,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
@@ -1210,7 +1388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
@@ -1240,7 +1418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1270,7 +1448,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1300,7 +1478,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1330,7 +1508,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
@@ -1360,7 +1538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>15</v>
       </c>
@@ -1390,7 +1568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>15</v>
       </c>
@@ -1420,7 +1598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>15</v>
       </c>
@@ -1450,7 +1628,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
@@ -1480,7 +1658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>15</v>
       </c>
@@ -1510,7 +1688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>14</v>
       </c>
@@ -1540,7 +1718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
@@ -1570,7 +1748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -1600,7 +1778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -1630,7 +1808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>15</v>
       </c>
@@ -1660,7 +1838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>15</v>
       </c>
@@ -1690,7 +1868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>20</v>
       </c>
@@ -1720,7 +1898,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
@@ -1750,7 +1928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>20</v>
       </c>
@@ -1780,7 +1958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>20</v>
       </c>
@@ -1810,7 +1988,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
         <v>20</v>
       </c>
@@ -1840,7 +2018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>20</v>
       </c>
@@ -1870,7 +2048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>20</v>
       </c>
@@ -1900,7 +2078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
@@ -1930,7 +2108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -1960,7 +2138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -1990,7 +2168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>20</v>
       </c>
@@ -2020,7 +2198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -2050,7 +2228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>44</v>
       </c>
@@ -2080,7 +2258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>44</v>
       </c>
@@ -2110,7 +2288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>44</v>
       </c>
@@ -2140,7 +2318,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>44</v>
       </c>
@@ -2170,7 +2348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>44</v>
       </c>
@@ -2200,7 +2378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>44</v>
       </c>
@@ -2230,7 +2408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="31" t="s">
         <v>15</v>
       </c>
@@ -2260,7 +2438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>15</v>
       </c>
@@ -2290,7 +2468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
         <v>15</v>
       </c>
@@ -2320,7 +2498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>15</v>
       </c>
@@ -2350,7 +2528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
         <v>15</v>
       </c>
@@ -2380,7 +2558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="s">
         <v>15</v>
       </c>
@@ -2410,7 +2588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>45</v>
       </c>
@@ -2440,7 +2618,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
@@ -2470,7 +2648,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>45</v>
       </c>
@@ -2500,7 +2678,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>45</v>
       </c>
@@ -2530,7 +2708,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>45</v>
       </c>
@@ -2560,7 +2738,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>45</v>
       </c>
@@ -2590,7 +2768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>46</v>
       </c>
@@ -2620,7 +2798,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>46</v>
       </c>
@@ -2650,7 +2828,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -2680,7 +2858,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>46</v>
       </c>
@@ -2710,7 +2888,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>46</v>
       </c>
@@ -2740,7 +2918,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>46</v>
       </c>
@@ -2770,7 +2948,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>20</v>
       </c>
@@ -2800,7 +2978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>20</v>
       </c>
@@ -2830,7 +3008,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>20</v>
       </c>
@@ -2860,7 +3038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>20</v>
       </c>
@@ -2890,7 +3068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>20</v>
       </c>
@@ -2920,7 +3098,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>20</v>
       </c>
@@ -2950,7 +3128,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -2980,7 +3158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>43</v>
       </c>
@@ -3010,7 +3188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>43</v>
       </c>
@@ -3040,7 +3218,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>43</v>
       </c>
@@ -3070,7 +3248,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>43</v>
       </c>
@@ -3100,7 +3278,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>43</v>
       </c>
@@ -3130,7 +3308,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>69</v>
       </c>
@@ -3160,7 +3338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
         <v>69</v>
       </c>
@@ -3190,7 +3368,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
         <v>69</v>
       </c>
@@ -3220,7 +3398,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
         <v>69</v>
       </c>
@@ -3250,7 +3428,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
         <v>69</v>
       </c>
@@ -3280,7 +3458,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
         <v>69</v>
       </c>
@@ -3310,7 +3488,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
         <v>69</v>
       </c>
@@ -3340,7 +3518,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
         <v>69</v>
       </c>
@@ -3370,7 +3548,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>68</v>
       </c>
@@ -3400,7 +3578,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>68</v>
       </c>
@@ -3430,7 +3608,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>68</v>
       </c>
@@ -3460,7 +3638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>68</v>
       </c>
@@ -3490,7 +3668,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>68</v>
       </c>
@@ -3520,7 +3698,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>68</v>
       </c>
@@ -3550,7 +3728,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>68</v>
       </c>
@@ -3580,7 +3758,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>68</v>
       </c>
@@ -3610,7 +3788,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
         <v>67</v>
       </c>
@@ -3640,7 +3818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
         <v>67</v>
       </c>
@@ -3670,7 +3848,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
         <v>67</v>
       </c>
@@ -3700,7 +3878,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
         <v>67</v>
       </c>
@@ -3730,7 +3908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="25" t="s">
         <v>67</v>
       </c>
@@ -3760,7 +3938,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="25" t="s">
         <v>67</v>
       </c>
@@ -3790,7 +3968,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="25" t="s">
         <v>67</v>
       </c>
@@ -3820,7 +3998,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="25" t="s">
         <v>67</v>
       </c>
@@ -3850,7 +4028,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="31" t="s">
         <v>66</v>
       </c>
@@ -3880,7 +4058,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="31" t="s">
         <v>66</v>
       </c>
@@ -3910,7 +4088,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="31" t="s">
         <v>66</v>
       </c>
@@ -3940,7 +4118,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="31" t="s">
         <v>66</v>
       </c>
@@ -3970,7 +4148,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="31" t="s">
         <v>66</v>
       </c>
@@ -4000,7 +4178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="31" t="s">
         <v>66</v>
       </c>
@@ -4030,7 +4208,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="31" t="s">
         <v>66</v>
       </c>
@@ -4060,7 +4238,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="31" t="s">
         <v>66</v>
       </c>
@@ -4090,7 +4268,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>20</v>
       </c>
@@ -4120,7 +4298,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>20</v>
       </c>
@@ -4150,7 +4328,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>20</v>
       </c>
@@ -4180,7 +4358,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>20</v>
       </c>
@@ -4210,7 +4388,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>20</v>
       </c>
@@ -4240,7 +4418,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>20</v>
       </c>
@@ -4270,7 +4448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>20</v>
       </c>
@@ -4300,7 +4478,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>20</v>
       </c>
@@ -4330,7 +4508,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="31" t="s">
         <v>66</v>
       </c>
@@ -4360,7 +4538,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="31" t="s">
         <v>66</v>
       </c>
@@ -4390,7 +4568,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="31" t="s">
         <v>66</v>
       </c>
@@ -4420,7 +4598,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="31" t="s">
         <v>66</v>
       </c>
@@ -4450,7 +4628,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="31" t="s">
         <v>66</v>
       </c>
@@ -4480,7 +4658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="31" t="s">
         <v>66</v>
       </c>
@@ -4510,7 +4688,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="31" t="s">
         <v>66</v>
       </c>
@@ -4540,7 +4718,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="31" t="s">
         <v>66</v>
       </c>
@@ -4570,7 +4748,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
         <v>46</v>
       </c>
@@ -4600,7 +4778,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>46</v>
       </c>
@@ -4630,7 +4808,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
         <v>46</v>
       </c>
@@ -4660,7 +4838,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>46</v>
       </c>
@@ -4690,7 +4868,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
         <v>46</v>
       </c>
@@ -4720,7 +4898,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>46</v>
       </c>
@@ -4750,7 +4928,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>46</v>
       </c>
@@ -4780,7 +4958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>46</v>
       </c>
@@ -4810,7 +4988,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>45</v>
       </c>
@@ -4840,7 +5018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>45</v>
       </c>
@@ -4870,7 +5048,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>45</v>
       </c>
@@ -4900,7 +5078,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>45</v>
       </c>
@@ -4930,7 +5108,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>45</v>
       </c>
@@ -4960,7 +5138,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>45</v>
       </c>
@@ -4990,7 +5168,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>45</v>
       </c>
@@ -5020,7 +5198,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>45</v>
       </c>
@@ -5050,7 +5228,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="20" t="s">
         <v>73</v>
       </c>
@@ -5080,7 +5258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="20" t="s">
         <v>73</v>
       </c>
@@ -5110,7 +5288,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="20" t="s">
         <v>73</v>
       </c>
@@ -5140,7 +5318,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="20" t="s">
         <v>73</v>
       </c>
@@ -5170,7 +5348,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="s">
         <v>73</v>
       </c>
@@ -5200,7 +5378,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="s">
         <v>73</v>
       </c>
@@ -5230,7 +5408,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="s">
         <v>73</v>
       </c>
@@ -5260,7 +5438,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="20" t="s">
         <v>73</v>
       </c>
@@ -5290,7 +5468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="33" t="s">
         <v>76</v>
       </c>
@@ -5320,7 +5498,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="33" t="s">
         <v>76</v>
       </c>
@@ -5350,7 +5528,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="33" t="s">
         <v>76</v>
       </c>
@@ -5380,7 +5558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="33" t="s">
         <v>76</v>
       </c>
@@ -5410,7 +5588,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="33" t="s">
         <v>76</v>
       </c>
@@ -5440,7 +5618,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="33" t="s">
         <v>76</v>
       </c>
@@ -5470,7 +5648,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="33" t="s">
         <v>76</v>
       </c>
@@ -5500,7 +5678,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="33" t="s">
         <v>76</v>
       </c>
@@ -5530,7 +5708,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="14" t="s">
         <v>74</v>
       </c>
@@ -5560,7 +5738,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="14" t="s">
         <v>74</v>
       </c>
@@ -5590,7 +5768,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
         <v>74</v>
       </c>
@@ -5620,7 +5798,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
         <v>74</v>
       </c>
@@ -5650,7 +5828,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
         <v>74</v>
       </c>
@@ -5680,7 +5858,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="14" t="s">
         <v>74</v>
       </c>
@@ -5710,7 +5888,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="14" t="s">
         <v>74</v>
       </c>
@@ -5740,7 +5918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="14" t="s">
         <v>74</v>
       </c>
@@ -5770,7 +5948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>82</v>
       </c>
@@ -5800,7 +5978,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>82</v>
       </c>
@@ -5830,7 +6008,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>82</v>
       </c>
@@ -5860,7 +6038,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>82</v>
       </c>
@@ -5890,7 +6068,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>82</v>
       </c>
@@ -5920,7 +6098,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>82</v>
       </c>
@@ -5950,7 +6128,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>82</v>
       </c>
@@ -5980,7 +6158,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>82</v>
       </c>
@@ -6010,7 +6188,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="33" t="s">
         <v>87</v>
       </c>
@@ -6040,7 +6218,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="33" t="s">
         <v>87</v>
       </c>
@@ -6070,7 +6248,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="33" t="s">
         <v>87</v>
       </c>
@@ -6100,7 +6278,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="33" t="s">
         <v>87</v>
       </c>
@@ -6130,7 +6308,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="33" t="s">
         <v>87</v>
       </c>
@@ -6160,7 +6338,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="33" t="s">
         <v>87</v>
       </c>
@@ -6190,7 +6368,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="33" t="s">
         <v>87</v>
       </c>
@@ -6220,7 +6398,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="33" t="s">
         <v>87</v>
       </c>
@@ -6250,7 +6428,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="s">
         <v>83</v>
       </c>
@@ -6280,7 +6458,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="20" t="s">
         <v>83</v>
       </c>
@@ -6310,7 +6488,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="20" t="s">
         <v>83</v>
       </c>
@@ -6340,7 +6518,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="20" t="s">
         <v>83</v>
       </c>
@@ -6370,7 +6548,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="s">
         <v>83</v>
       </c>
@@ -6400,7 +6578,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="20" t="s">
         <v>83</v>
       </c>
@@ -6430,7 +6608,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="20" t="s">
         <v>83</v>
       </c>
@@ -6460,7 +6638,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="20" t="s">
         <v>83</v>
       </c>
@@ -6490,7 +6668,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
         <v>84</v>
       </c>
@@ -6517,10 +6695,10 @@
         <v>-6.3663800000000003E-4</v>
       </c>
       <c r="I180" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
         <v>84</v>
       </c>
@@ -6547,10 +6725,10 @@
         <v>5.4114230000000003E-3</v>
       </c>
       <c r="I181" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
         <v>84</v>
       </c>
@@ -6577,10 +6755,10 @@
         <v>2.7375434000000001E-2</v>
       </c>
       <c r="I182" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
         <v>84</v>
       </c>
@@ -6607,10 +6785,10 @@
         <v>6.8756904000000008E-2</v>
       </c>
       <c r="I183" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
         <v>84</v>
       </c>
@@ -6637,10 +6815,10 @@
         <v>0.10727350300000002</v>
       </c>
       <c r="I184" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
         <v>84</v>
       </c>
@@ -6667,10 +6845,10 @@
         <v>0.15533967200000001</v>
       </c>
       <c r="I185" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
         <v>84</v>
       </c>
@@ -6697,10 +6875,10 @@
         <v>0.21231877300000002</v>
       </c>
       <c r="I186" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
         <v>84</v>
       </c>
@@ -6727,8 +6905,3255 @@
         <v>0.26388645100000002</v>
       </c>
       <c r="I187" s="17" t="s">
-        <v>70</v>
-      </c>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="6">
+        <v>60</v>
+      </c>
+      <c r="E188" s="8">
+        <v>0</v>
+      </c>
+      <c r="F188" s="9">
+        <v>0</v>
+      </c>
+      <c r="G188" s="8">
+        <v>18</v>
+      </c>
+      <c r="H188" s="10">
+        <f t="shared" ref="H188:H195" si="5">G188/1000*0.318319</f>
+        <v>5.7297419999999995E-3</v>
+      </c>
+      <c r="I188" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="6">
+        <v>60</v>
+      </c>
+      <c r="E189" s="8">
+        <v>1</v>
+      </c>
+      <c r="F189" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="G189" s="8">
+        <v>34</v>
+      </c>
+      <c r="H189" s="10">
+        <f t="shared" si="5"/>
+        <v>1.0822846000000001E-2</v>
+      </c>
+      <c r="I189" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="6">
+        <v>60</v>
+      </c>
+      <c r="E190" s="8">
+        <v>2</v>
+      </c>
+      <c r="F190" s="9">
+        <v>0.31</v>
+      </c>
+      <c r="G190" s="8">
+        <v>78</v>
+      </c>
+      <c r="H190" s="10">
+        <f t="shared" si="5"/>
+        <v>2.4828882E-2</v>
+      </c>
+      <c r="I190" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="6">
+        <v>60</v>
+      </c>
+      <c r="E191" s="8">
+        <v>3</v>
+      </c>
+      <c r="F191" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="G191" s="8">
+        <v>248</v>
+      </c>
+      <c r="H191" s="10">
+        <f t="shared" si="5"/>
+        <v>7.894311200000001E-2</v>
+      </c>
+      <c r="I191" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="6">
+        <v>60</v>
+      </c>
+      <c r="E192" s="8">
+        <v>4</v>
+      </c>
+      <c r="F192" s="9">
+        <v>0.59</v>
+      </c>
+      <c r="G192" s="8">
+        <v>387</v>
+      </c>
+      <c r="H192" s="10">
+        <f t="shared" si="5"/>
+        <v>0.123189453</v>
+      </c>
+      <c r="I192" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="6">
+        <v>60</v>
+      </c>
+      <c r="E193" s="8">
+        <v>5</v>
+      </c>
+      <c r="F193" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="G193" s="8">
+        <v>537</v>
+      </c>
+      <c r="H193" s="10">
+        <f t="shared" si="5"/>
+        <v>0.17093730300000001</v>
+      </c>
+      <c r="I193" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="6">
+        <v>60</v>
+      </c>
+      <c r="E194" s="8">
+        <v>7</v>
+      </c>
+      <c r="F194" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="G194" s="8">
+        <v>680</v>
+      </c>
+      <c r="H194" s="10">
+        <f t="shared" si="5"/>
+        <v>0.21645692000000002</v>
+      </c>
+      <c r="I194" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="6">
+        <v>60</v>
+      </c>
+      <c r="E195" s="8">
+        <v>10</v>
+      </c>
+      <c r="F195" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="G195" s="8">
+        <v>889</v>
+      </c>
+      <c r="H195" s="10">
+        <f t="shared" si="5"/>
+        <v>0.28298559100000004</v>
+      </c>
+      <c r="I195" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C196" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="31">
+        <v>60</v>
+      </c>
+      <c r="E196" s="33">
+        <v>0</v>
+      </c>
+      <c r="F196" s="34">
+        <v>0</v>
+      </c>
+      <c r="G196" s="33">
+        <v>18</v>
+      </c>
+      <c r="H196" s="35">
+        <f t="shared" ref="H196:H226" si="6">G196/1000*0.318319</f>
+        <v>5.7297419999999995E-3</v>
+      </c>
+      <c r="I196" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B197" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C197" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="31">
+        <v>60</v>
+      </c>
+      <c r="E197" s="33">
+        <v>1</v>
+      </c>
+      <c r="F197" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="G197" s="33">
+        <v>78</v>
+      </c>
+      <c r="H197" s="35">
+        <f t="shared" si="6"/>
+        <v>2.4828882E-2</v>
+      </c>
+      <c r="I197" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C198" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="31">
+        <v>60</v>
+      </c>
+      <c r="E198" s="33">
+        <v>2</v>
+      </c>
+      <c r="F198" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="G198" s="33">
+        <v>128</v>
+      </c>
+      <c r="H198" s="35">
+        <f t="shared" si="6"/>
+        <v>4.0744832000000002E-2</v>
+      </c>
+      <c r="I198" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B199" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C199" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D199" s="31">
+        <v>60</v>
+      </c>
+      <c r="E199" s="33">
+        <v>3</v>
+      </c>
+      <c r="F199" s="34">
+        <v>0.44</v>
+      </c>
+      <c r="G199" s="33">
+        <v>187</v>
+      </c>
+      <c r="H199" s="35">
+        <f t="shared" si="6"/>
+        <v>5.9525653000000005E-2</v>
+      </c>
+      <c r="I199" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B200" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C200" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" s="31">
+        <v>60</v>
+      </c>
+      <c r="E200" s="33">
+        <v>4</v>
+      </c>
+      <c r="F200" s="34">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G200" s="33">
+        <v>238</v>
+      </c>
+      <c r="H200" s="35">
+        <f t="shared" si="6"/>
+        <v>7.5759922000000007E-2</v>
+      </c>
+      <c r="I200" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B201" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C201" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D201" s="31">
+        <v>60</v>
+      </c>
+      <c r="E201" s="33">
+        <v>5</v>
+      </c>
+      <c r="F201" s="34">
+        <v>0.71</v>
+      </c>
+      <c r="G201" s="33">
+        <v>278</v>
+      </c>
+      <c r="H201" s="35">
+        <f t="shared" si="6"/>
+        <v>8.8492682000000017E-2</v>
+      </c>
+      <c r="I201" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B202" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C202" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D202" s="31">
+        <v>60</v>
+      </c>
+      <c r="E202" s="33">
+        <v>10</v>
+      </c>
+      <c r="F202" s="34">
+        <v>0.98</v>
+      </c>
+      <c r="G202" s="33">
+        <v>407</v>
+      </c>
+      <c r="H202" s="35">
+        <f t="shared" si="6"/>
+        <v>0.12955583300000001</v>
+      </c>
+      <c r="I202" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B203" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C203" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D203" s="18">
+        <v>60</v>
+      </c>
+      <c r="E203" s="20">
+        <v>0</v>
+      </c>
+      <c r="F203" s="21">
+        <v>0</v>
+      </c>
+      <c r="G203" s="20">
+        <v>0</v>
+      </c>
+      <c r="H203" s="22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I203" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B204" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C204" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D204" s="18">
+        <v>60</v>
+      </c>
+      <c r="E204" s="20">
+        <v>1</v>
+      </c>
+      <c r="F204" s="21">
+        <v>0.16</v>
+      </c>
+      <c r="G204" s="20">
+        <v>20</v>
+      </c>
+      <c r="H204" s="22">
+        <f t="shared" si="6"/>
+        <v>6.3663800000000005E-3</v>
+      </c>
+      <c r="I204" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B205" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C205" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="18">
+        <v>60</v>
+      </c>
+      <c r="E205" s="20">
+        <v>2</v>
+      </c>
+      <c r="F205" s="21">
+        <v>0.31</v>
+      </c>
+      <c r="G205" s="20">
+        <v>139</v>
+      </c>
+      <c r="H205" s="22">
+        <f t="shared" si="6"/>
+        <v>4.4246341000000008E-2</v>
+      </c>
+      <c r="I205" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B206" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C206" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D206" s="18">
+        <v>60</v>
+      </c>
+      <c r="E206" s="20">
+        <v>3</v>
+      </c>
+      <c r="F206" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="G206" s="20">
+        <v>398</v>
+      </c>
+      <c r="H206" s="22">
+        <f t="shared" si="6"/>
+        <v>0.12669096200000002</v>
+      </c>
+      <c r="I206" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B207" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C207" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="18">
+        <v>60</v>
+      </c>
+      <c r="E207" s="20">
+        <v>4</v>
+      </c>
+      <c r="F207" s="21">
+        <v>0.59</v>
+      </c>
+      <c r="G207" s="20">
+        <v>569</v>
+      </c>
+      <c r="H207" s="22">
+        <f t="shared" si="6"/>
+        <v>0.18112351099999999</v>
+      </c>
+      <c r="I207" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B208" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C208" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D208" s="18">
+        <v>60</v>
+      </c>
+      <c r="E208" s="20">
+        <v>5</v>
+      </c>
+      <c r="F208" s="21">
+        <v>0.72</v>
+      </c>
+      <c r="G208" s="20">
+        <v>741</v>
+      </c>
+      <c r="H208" s="22">
+        <f t="shared" si="6"/>
+        <v>0.23587437900000002</v>
+      </c>
+      <c r="I208" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B209" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C209" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D209" s="18">
+        <v>60</v>
+      </c>
+      <c r="E209" s="20">
+        <v>7</v>
+      </c>
+      <c r="F209" s="21">
+        <v>0.88</v>
+      </c>
+      <c r="G209" s="20">
+        <v>950</v>
+      </c>
+      <c r="H209" s="22">
+        <f t="shared" si="6"/>
+        <v>0.30240305000000001</v>
+      </c>
+      <c r="I209" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B210" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C210" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D210" s="18">
+        <v>60</v>
+      </c>
+      <c r="E210" s="20">
+        <v>10</v>
+      </c>
+      <c r="F210" s="21">
+        <v>0.99</v>
+      </c>
+      <c r="G210" s="20">
+        <v>1111</v>
+      </c>
+      <c r="H210" s="22">
+        <f t="shared" si="6"/>
+        <v>0.353652409</v>
+      </c>
+      <c r="I210" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B211" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D211" s="12">
+        <v>60</v>
+      </c>
+      <c r="E211" s="14">
+        <v>0</v>
+      </c>
+      <c r="F211" s="15">
+        <v>0</v>
+      </c>
+      <c r="G211" s="14">
+        <v>25</v>
+      </c>
+      <c r="H211" s="16">
+        <f t="shared" si="6"/>
+        <v>7.9579750000000008E-3</v>
+      </c>
+      <c r="I211" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C212" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="12">
+        <v>60</v>
+      </c>
+      <c r="E212" s="14">
+        <v>1</v>
+      </c>
+      <c r="F212" s="15">
+        <v>0.16</v>
+      </c>
+      <c r="G212" s="14">
+        <v>77</v>
+      </c>
+      <c r="H212" s="16">
+        <f t="shared" si="6"/>
+        <v>2.4510563000000003E-2</v>
+      </c>
+      <c r="I212" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B213" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C213" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" s="12">
+        <v>60</v>
+      </c>
+      <c r="E213" s="14">
+        <v>2</v>
+      </c>
+      <c r="F213" s="15">
+        <v>0.31</v>
+      </c>
+      <c r="G213" s="14">
+        <v>157</v>
+      </c>
+      <c r="H213" s="16">
+        <f t="shared" si="6"/>
+        <v>4.9976083000000004E-2</v>
+      </c>
+      <c r="I213" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C214" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D214" s="12">
+        <v>60</v>
+      </c>
+      <c r="E214" s="14">
+        <v>3</v>
+      </c>
+      <c r="F214" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="G214" s="14">
+        <v>318</v>
+      </c>
+      <c r="H214" s="16">
+        <f t="shared" si="6"/>
+        <v>0.10122544200000001</v>
+      </c>
+      <c r="I214" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B215" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C215" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" s="12">
+        <v>60</v>
+      </c>
+      <c r="E215" s="14">
+        <v>4</v>
+      </c>
+      <c r="F215" s="15">
+        <v>0.59</v>
+      </c>
+      <c r="G215" s="14">
+        <v>428</v>
+      </c>
+      <c r="H215" s="16">
+        <f t="shared" si="6"/>
+        <v>0.136240532</v>
+      </c>
+      <c r="I215" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="12">
+        <v>60</v>
+      </c>
+      <c r="E216" s="14">
+        <v>5</v>
+      </c>
+      <c r="F216" s="15">
+        <v>0.72</v>
+      </c>
+      <c r="G216" s="14">
+        <v>557</v>
+      </c>
+      <c r="H216" s="16">
+        <f t="shared" si="6"/>
+        <v>0.17730368300000002</v>
+      </c>
+      <c r="I216" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B217" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C217" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="12">
+        <v>60</v>
+      </c>
+      <c r="E217" s="14">
+        <v>7</v>
+      </c>
+      <c r="F217" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="G217" s="14">
+        <v>768</v>
+      </c>
+      <c r="H217" s="16">
+        <f t="shared" si="6"/>
+        <v>0.24446899200000002</v>
+      </c>
+      <c r="I217" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C218" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="12">
+        <v>60</v>
+      </c>
+      <c r="E218" s="14">
+        <v>10</v>
+      </c>
+      <c r="F218" s="15">
+        <v>0.99</v>
+      </c>
+      <c r="G218" s="14">
+        <v>840</v>
+      </c>
+      <c r="H218" s="16">
+        <f t="shared" si="6"/>
+        <v>0.26738795999999998</v>
+      </c>
+      <c r="I218" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C219" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="6">
+        <v>60</v>
+      </c>
+      <c r="E219" s="8">
+        <v>0</v>
+      </c>
+      <c r="F219" s="9">
+        <v>0</v>
+      </c>
+      <c r="G219" s="8">
+        <v>-12</v>
+      </c>
+      <c r="H219" s="10">
+        <f t="shared" si="6"/>
+        <v>-3.8198280000000004E-3</v>
+      </c>
+      <c r="I219" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C220" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" s="6">
+        <v>60</v>
+      </c>
+      <c r="E220" s="8">
+        <v>1</v>
+      </c>
+      <c r="F220" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="G220" s="8">
+        <v>8</v>
+      </c>
+      <c r="H220" s="10">
+        <f t="shared" si="6"/>
+        <v>2.5465520000000001E-3</v>
+      </c>
+      <c r="I220" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D221" s="6">
+        <v>60</v>
+      </c>
+      <c r="E221" s="8">
+        <v>2</v>
+      </c>
+      <c r="F221" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="G221" s="8">
+        <v>66</v>
+      </c>
+      <c r="H221" s="10">
+        <f t="shared" si="6"/>
+        <v>2.1009054000000003E-2</v>
+      </c>
+      <c r="I221" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C222" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="6">
+        <v>60</v>
+      </c>
+      <c r="E222" s="8">
+        <v>3</v>
+      </c>
+      <c r="F222" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="G222" s="8">
+        <v>216</v>
+      </c>
+      <c r="H222" s="10">
+        <f t="shared" si="6"/>
+        <v>6.8756904000000008E-2</v>
+      </c>
+      <c r="I222" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="6">
+        <v>60</v>
+      </c>
+      <c r="E223" s="8">
+        <v>4</v>
+      </c>
+      <c r="F223" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G223" s="8">
+        <v>396</v>
+      </c>
+      <c r="H223" s="10">
+        <f t="shared" si="6"/>
+        <v>0.12605432400000002</v>
+      </c>
+      <c r="I223" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C224" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="6">
+        <v>60</v>
+      </c>
+      <c r="E224" s="8">
+        <v>5</v>
+      </c>
+      <c r="F224" s="9">
+        <v>0.71</v>
+      </c>
+      <c r="G224" s="8">
+        <v>527</v>
+      </c>
+      <c r="H224" s="10">
+        <f t="shared" si="6"/>
+        <v>0.16775411300000001</v>
+      </c>
+      <c r="I224" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="6">
+        <v>60</v>
+      </c>
+      <c r="E225" s="8">
+        <v>7</v>
+      </c>
+      <c r="F225" s="9">
+        <v>0.87</v>
+      </c>
+      <c r="G225" s="8">
+        <v>626</v>
+      </c>
+      <c r="H225" s="10">
+        <f t="shared" si="6"/>
+        <v>0.19926769400000002</v>
+      </c>
+      <c r="I225" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="6">
+        <v>60</v>
+      </c>
+      <c r="E226" s="8">
+        <v>10</v>
+      </c>
+      <c r="F226" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="G226" s="8">
+        <v>750</v>
+      </c>
+      <c r="H226" s="10">
+        <f t="shared" si="6"/>
+        <v>0.23873925000000001</v>
+      </c>
+      <c r="I226" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B227" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C227" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D227" s="31">
+        <v>60</v>
+      </c>
+      <c r="E227" s="33">
+        <v>0</v>
+      </c>
+      <c r="F227" s="34">
+        <v>0</v>
+      </c>
+      <c r="G227" s="33">
+        <v>57</v>
+      </c>
+      <c r="H227" s="35">
+        <f t="shared" ref="H227:H257" si="7">G227/1000*0.318319</f>
+        <v>1.8144183000000001E-2</v>
+      </c>
+      <c r="I227" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C228" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" s="31">
+        <v>60</v>
+      </c>
+      <c r="E228" s="33">
+        <v>1</v>
+      </c>
+      <c r="F228" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="G228" s="33">
+        <v>226</v>
+      </c>
+      <c r="H228" s="35">
+        <f t="shared" si="7"/>
+        <v>7.194009400000001E-2</v>
+      </c>
+      <c r="I228" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B229" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C229" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" s="31">
+        <v>60</v>
+      </c>
+      <c r="E229" s="33">
+        <v>2</v>
+      </c>
+      <c r="F229" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="G229" s="33">
+        <v>376</v>
+      </c>
+      <c r="H229" s="35">
+        <f t="shared" si="7"/>
+        <v>0.119687944</v>
+      </c>
+      <c r="I229" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B230" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C230" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" s="31">
+        <v>60</v>
+      </c>
+      <c r="E230" s="33">
+        <v>3</v>
+      </c>
+      <c r="F230" s="34">
+        <v>0.44</v>
+      </c>
+      <c r="G230" s="33">
+        <v>477</v>
+      </c>
+      <c r="H230" s="35">
+        <f t="shared" si="7"/>
+        <v>0.151838163</v>
+      </c>
+      <c r="I230" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B231" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C231" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" s="31">
+        <v>60</v>
+      </c>
+      <c r="E231" s="33">
+        <v>4</v>
+      </c>
+      <c r="F231" s="34">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G231" s="33">
+        <v>587</v>
+      </c>
+      <c r="H231" s="35">
+        <f t="shared" si="7"/>
+        <v>0.186853253</v>
+      </c>
+      <c r="I231" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B232" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C232" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D232" s="31">
+        <v>60</v>
+      </c>
+      <c r="E232" s="33">
+        <v>5</v>
+      </c>
+      <c r="F232" s="34">
+        <v>0.7</v>
+      </c>
+      <c r="G232" s="33">
+        <v>720</v>
+      </c>
+      <c r="H232" s="35">
+        <f t="shared" si="7"/>
+        <v>0.22918968000000001</v>
+      </c>
+      <c r="I232" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B233" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C233" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D233" s="31">
+        <v>60</v>
+      </c>
+      <c r="E233" s="33">
+        <v>7</v>
+      </c>
+      <c r="F233" s="34">
+        <v>0.88</v>
+      </c>
+      <c r="G233" s="33">
+        <v>898</v>
+      </c>
+      <c r="H233" s="35">
+        <f t="shared" ref="H233" si="8">G233/1000*0.318319</f>
+        <v>0.28585046200000003</v>
+      </c>
+      <c r="I233" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C234" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D234" s="31">
+        <v>60</v>
+      </c>
+      <c r="E234" s="33">
+        <v>10</v>
+      </c>
+      <c r="F234" s="34">
+        <v>0.98</v>
+      </c>
+      <c r="G234" s="33">
+        <v>988</v>
+      </c>
+      <c r="H234" s="35">
+        <f t="shared" si="7"/>
+        <v>0.31449917199999999</v>
+      </c>
+      <c r="I234" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B235" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C235" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" s="18">
+        <v>60</v>
+      </c>
+      <c r="E235" s="20">
+        <v>0</v>
+      </c>
+      <c r="F235" s="21">
+        <v>0</v>
+      </c>
+      <c r="G235" s="20">
+        <v>18</v>
+      </c>
+      <c r="H235" s="22">
+        <f t="shared" si="7"/>
+        <v>5.7297419999999995E-3</v>
+      </c>
+      <c r="I235" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B236" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C236" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D236" s="18">
+        <v>60</v>
+      </c>
+      <c r="E236" s="20">
+        <v>1</v>
+      </c>
+      <c r="F236" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="G236" s="20">
+        <v>36</v>
+      </c>
+      <c r="H236" s="22">
+        <f t="shared" si="7"/>
+        <v>1.1459483999999999E-2</v>
+      </c>
+      <c r="I236" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B237" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C237" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D237" s="18">
+        <v>60</v>
+      </c>
+      <c r="E237" s="20">
+        <v>2</v>
+      </c>
+      <c r="F237" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G237" s="20">
+        <v>247</v>
+      </c>
+      <c r="H237" s="22">
+        <f t="shared" si="7"/>
+        <v>7.8624792999999998E-2</v>
+      </c>
+      <c r="I237" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B238" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C238" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" s="18">
+        <v>60</v>
+      </c>
+      <c r="E238" s="20">
+        <v>3</v>
+      </c>
+      <c r="F238" s="21">
+        <v>0.44</v>
+      </c>
+      <c r="G238" s="20">
+        <v>436</v>
+      </c>
+      <c r="H238" s="22">
+        <f t="shared" si="7"/>
+        <v>0.13878708400000001</v>
+      </c>
+      <c r="I238" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B239" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C239" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D239" s="18">
+        <v>60</v>
+      </c>
+      <c r="E239" s="20">
+        <v>4</v>
+      </c>
+      <c r="F239" s="21">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G239" s="20">
+        <v>678</v>
+      </c>
+      <c r="H239" s="22">
+        <f t="shared" si="7"/>
+        <v>0.21582028200000003</v>
+      </c>
+      <c r="I239" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B240" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C240" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D240" s="18">
+        <v>60</v>
+      </c>
+      <c r="E240" s="20">
+        <v>5</v>
+      </c>
+      <c r="F240" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="G240" s="20">
+        <v>839</v>
+      </c>
+      <c r="H240" s="22">
+        <f t="shared" si="7"/>
+        <v>0.26706964100000002</v>
+      </c>
+      <c r="I240" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B241" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C241" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D241" s="18">
+        <v>60</v>
+      </c>
+      <c r="E241" s="20">
+        <v>7</v>
+      </c>
+      <c r="F241" s="21">
+        <v>0.87</v>
+      </c>
+      <c r="G241" s="20">
+        <v>1090</v>
+      </c>
+      <c r="H241" s="22">
+        <f t="shared" si="7"/>
+        <v>0.34696771000000004</v>
+      </c>
+      <c r="I241" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B242" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C242" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D242" s="18">
+        <v>60</v>
+      </c>
+      <c r="E242" s="20">
+        <v>10</v>
+      </c>
+      <c r="F242" s="21">
+        <v>0.98</v>
+      </c>
+      <c r="G242" s="20">
+        <v>1270</v>
+      </c>
+      <c r="H242" s="22">
+        <f t="shared" si="7"/>
+        <v>0.40426513000000003</v>
+      </c>
+      <c r="I242" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B243" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C243" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D243" s="12">
+        <v>60</v>
+      </c>
+      <c r="E243" s="14">
+        <v>0</v>
+      </c>
+      <c r="F243" s="15">
+        <v>0</v>
+      </c>
+      <c r="G243" s="14">
+        <v>0</v>
+      </c>
+      <c r="H243" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I243" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C244" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D244" s="12">
+        <v>60</v>
+      </c>
+      <c r="E244" s="14">
+        <v>1</v>
+      </c>
+      <c r="F244" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="G244" s="14">
+        <v>18</v>
+      </c>
+      <c r="H244" s="16">
+        <f t="shared" si="7"/>
+        <v>5.7297419999999995E-3</v>
+      </c>
+      <c r="I244" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B245" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C245" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D245" s="12">
+        <v>60</v>
+      </c>
+      <c r="E245" s="14">
+        <v>2</v>
+      </c>
+      <c r="F245" s="15">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G245" s="14">
+        <v>87</v>
+      </c>
+      <c r="H245" s="16">
+        <f t="shared" si="7"/>
+        <v>2.7693752999999998E-2</v>
+      </c>
+      <c r="I245" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C246" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" s="12">
+        <v>60</v>
+      </c>
+      <c r="E246" s="14">
+        <v>3</v>
+      </c>
+      <c r="F246" s="15">
+        <v>0.43</v>
+      </c>
+      <c r="G246" s="14">
+        <v>146</v>
+      </c>
+      <c r="H246" s="16">
+        <f t="shared" si="7"/>
+        <v>4.6474573999999998E-2</v>
+      </c>
+      <c r="I246" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B247" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C247" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D247" s="12">
+        <v>60</v>
+      </c>
+      <c r="E247" s="14">
+        <v>4</v>
+      </c>
+      <c r="F247" s="15">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G247" s="14">
+        <v>237</v>
+      </c>
+      <c r="H247" s="16">
+        <f t="shared" si="7"/>
+        <v>7.5441602999999996E-2</v>
+      </c>
+      <c r="I247" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C248" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D248" s="12">
+        <v>60</v>
+      </c>
+      <c r="E248" s="14">
+        <v>5</v>
+      </c>
+      <c r="F248" s="15">
+        <v>0.69</v>
+      </c>
+      <c r="G248" s="14">
+        <v>337</v>
+      </c>
+      <c r="H248" s="16">
+        <f t="shared" si="7"/>
+        <v>0.10727350300000002</v>
+      </c>
+      <c r="I248" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B249" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C249" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D249" s="12">
+        <v>60</v>
+      </c>
+      <c r="E249" s="14">
+        <v>7</v>
+      </c>
+      <c r="F249" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="G249" s="14">
+        <v>457</v>
+      </c>
+      <c r="H249" s="16">
+        <f t="shared" si="7"/>
+        <v>0.14547178300000002</v>
+      </c>
+      <c r="I249" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C250" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" s="12">
+        <v>60</v>
+      </c>
+      <c r="E250" s="14">
+        <v>10</v>
+      </c>
+      <c r="F250" s="15">
+        <v>0.96</v>
+      </c>
+      <c r="G250" s="14">
+        <v>526</v>
+      </c>
+      <c r="H250" s="16">
+        <f t="shared" si="7"/>
+        <v>0.16743579400000003</v>
+      </c>
+      <c r="I250" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C251" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D251" s="6">
+        <v>60</v>
+      </c>
+      <c r="E251" s="8">
+        <v>0</v>
+      </c>
+      <c r="F251" s="9">
+        <v>0</v>
+      </c>
+      <c r="G251" s="8">
+        <v>17</v>
+      </c>
+      <c r="H251" s="10">
+        <f t="shared" si="7"/>
+        <v>5.4114230000000003E-3</v>
+      </c>
+      <c r="I251" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B252" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C252" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252" s="6">
+        <v>60</v>
+      </c>
+      <c r="E252" s="8">
+        <v>2</v>
+      </c>
+      <c r="F252" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G252" s="8">
+        <v>107</v>
+      </c>
+      <c r="H252" s="10">
+        <f t="shared" si="7"/>
+        <v>3.4060132999999999E-2</v>
+      </c>
+      <c r="I252" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C253" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="6">
+        <v>60</v>
+      </c>
+      <c r="E253" s="8">
+        <v>3</v>
+      </c>
+      <c r="F253" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="G253" s="8">
+        <v>187</v>
+      </c>
+      <c r="H253" s="10">
+        <f t="shared" si="7"/>
+        <v>5.9525653000000005E-2</v>
+      </c>
+      <c r="I253" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C254" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="6">
+        <v>60</v>
+      </c>
+      <c r="E254" s="8">
+        <v>4</v>
+      </c>
+      <c r="F254" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G254" s="8">
+        <v>266</v>
+      </c>
+      <c r="H254" s="10">
+        <f t="shared" si="7"/>
+        <v>8.4672854000000006E-2</v>
+      </c>
+      <c r="I254" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C255" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="6">
+        <v>60</v>
+      </c>
+      <c r="E255" s="8">
+        <v>5</v>
+      </c>
+      <c r="F255" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="G255" s="8">
+        <v>367</v>
+      </c>
+      <c r="H255" s="10">
+        <f t="shared" si="7"/>
+        <v>0.116823073</v>
+      </c>
+      <c r="I255" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="6">
+        <v>60</v>
+      </c>
+      <c r="E256" s="8">
+        <v>7</v>
+      </c>
+      <c r="F256" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="G256" s="8">
+        <v>479</v>
+      </c>
+      <c r="H256" s="10">
+        <f t="shared" si="7"/>
+        <v>0.15247480099999999</v>
+      </c>
+      <c r="I256" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="6">
+        <v>60</v>
+      </c>
+      <c r="E257" s="8">
+        <v>10</v>
+      </c>
+      <c r="F257" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="G257" s="8">
+        <v>527</v>
+      </c>
+      <c r="H257" s="10">
+        <f t="shared" si="7"/>
+        <v>0.16775411300000001</v>
+      </c>
+      <c r="I257" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C258" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258" s="31">
+        <v>60</v>
+      </c>
+      <c r="E258" s="33">
+        <v>0</v>
+      </c>
+      <c r="F258" s="34">
+        <v>0</v>
+      </c>
+      <c r="G258" s="33">
+        <v>8</v>
+      </c>
+      <c r="H258" s="35">
+        <f t="shared" ref="H258:H289" si="9">G258/1000*0.318319</f>
+        <v>2.5465520000000001E-3</v>
+      </c>
+      <c r="I258" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B259" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C259" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D259" s="31">
+        <v>60</v>
+      </c>
+      <c r="E259" s="33">
+        <v>1</v>
+      </c>
+      <c r="F259" s="34">
+        <v>0.16</v>
+      </c>
+      <c r="G259" s="33">
+        <v>20</v>
+      </c>
+      <c r="H259" s="35">
+        <f t="shared" si="9"/>
+        <v>6.3663800000000005E-3</v>
+      </c>
+      <c r="I259" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B260" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C260" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D260" s="31">
+        <v>60</v>
+      </c>
+      <c r="E260" s="33">
+        <v>2</v>
+      </c>
+      <c r="F260" s="34">
+        <v>0.31</v>
+      </c>
+      <c r="G260" s="33">
+        <v>108</v>
+      </c>
+      <c r="H260" s="35">
+        <f t="shared" si="9"/>
+        <v>3.4378452000000004E-2</v>
+      </c>
+      <c r="I260" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B261" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C261" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D261" s="31">
+        <v>60</v>
+      </c>
+      <c r="E261" s="33">
+        <v>3</v>
+      </c>
+      <c r="F261" s="34">
+        <v>0.46</v>
+      </c>
+      <c r="G261" s="33">
+        <v>209</v>
+      </c>
+      <c r="H261" s="35">
+        <f t="shared" si="9"/>
+        <v>6.6528670999999998E-2</v>
+      </c>
+      <c r="I261" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B262" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C262" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D262" s="31">
+        <v>60</v>
+      </c>
+      <c r="E262" s="33">
+        <v>4</v>
+      </c>
+      <c r="F262" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="G262" s="33">
+        <v>316</v>
+      </c>
+      <c r="H262" s="35">
+        <f t="shared" si="9"/>
+        <v>0.100588804</v>
+      </c>
+      <c r="I262" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B263" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C263" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D263" s="31">
+        <v>60</v>
+      </c>
+      <c r="E263" s="33">
+        <v>5</v>
+      </c>
+      <c r="F263" s="34">
+        <v>0.73</v>
+      </c>
+      <c r="G263" s="33">
+        <v>448</v>
+      </c>
+      <c r="H263" s="35">
+        <f t="shared" si="9"/>
+        <v>0.142606912</v>
+      </c>
+      <c r="I263" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C264" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D264" s="31">
+        <v>60</v>
+      </c>
+      <c r="E264" s="33">
+        <v>7</v>
+      </c>
+      <c r="F264" s="34">
+        <v>0.9</v>
+      </c>
+      <c r="G264" s="33">
+        <v>559</v>
+      </c>
+      <c r="H264" s="35">
+        <f t="shared" si="9"/>
+        <v>0.17794032100000004</v>
+      </c>
+      <c r="I264" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B265" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C265" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D265" s="31">
+        <v>60</v>
+      </c>
+      <c r="E265" s="33">
+        <v>10</v>
+      </c>
+      <c r="F265" s="34">
+        <v>1</v>
+      </c>
+      <c r="G265" s="33">
+        <v>632</v>
+      </c>
+      <c r="H265" s="35">
+        <f t="shared" si="9"/>
+        <v>0.20117760800000001</v>
+      </c>
+      <c r="I265" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C266" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D266" s="12">
+        <v>60</v>
+      </c>
+      <c r="E266" s="14">
+        <v>0</v>
+      </c>
+      <c r="F266" s="15">
+        <v>0</v>
+      </c>
+      <c r="G266" s="14">
+        <v>38</v>
+      </c>
+      <c r="H266" s="16">
+        <f t="shared" si="9"/>
+        <v>1.2096122000000001E-2</v>
+      </c>
+      <c r="I266" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B267" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C267" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D267" s="12">
+        <v>60</v>
+      </c>
+      <c r="E267" s="14">
+        <v>1</v>
+      </c>
+      <c r="F267" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="G267" s="14">
+        <v>68</v>
+      </c>
+      <c r="H267" s="16">
+        <f t="shared" si="9"/>
+        <v>2.1645692000000001E-2</v>
+      </c>
+      <c r="I267" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C268" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D268" s="12">
+        <v>60</v>
+      </c>
+      <c r="E268" s="14">
+        <v>2</v>
+      </c>
+      <c r="F268" s="15">
+        <v>0.31</v>
+      </c>
+      <c r="G268" s="14">
+        <v>129</v>
+      </c>
+      <c r="H268" s="16">
+        <f t="shared" si="9"/>
+        <v>4.1063151000000006E-2</v>
+      </c>
+      <c r="I268" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B269" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C269" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" s="12">
+        <v>60</v>
+      </c>
+      <c r="E269" s="14">
+        <v>3</v>
+      </c>
+      <c r="F269" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="G269" s="14">
+        <v>210</v>
+      </c>
+      <c r="H269" s="16">
+        <f t="shared" si="9"/>
+        <v>6.6846989999999995E-2</v>
+      </c>
+      <c r="I269" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C270" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="12">
+        <v>60</v>
+      </c>
+      <c r="E270" s="14">
+        <v>4</v>
+      </c>
+      <c r="F270" s="15">
+        <v>0.59</v>
+      </c>
+      <c r="G270" s="14">
+        <v>288</v>
+      </c>
+      <c r="H270" s="16">
+        <f t="shared" si="9"/>
+        <v>9.1675871999999992E-2</v>
+      </c>
+      <c r="I270" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B271" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C271" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D271" s="12">
+        <v>60</v>
+      </c>
+      <c r="E271" s="14">
+        <v>5</v>
+      </c>
+      <c r="F271" s="15">
+        <v>0.72</v>
+      </c>
+      <c r="G271" s="14">
+        <v>380</v>
+      </c>
+      <c r="H271" s="16">
+        <f t="shared" si="9"/>
+        <v>0.12096122000000001</v>
+      </c>
+      <c r="I271" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C272" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D272" s="12">
+        <v>60</v>
+      </c>
+      <c r="E272" s="14">
+        <v>7</v>
+      </c>
+      <c r="F272" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="G272" s="14">
+        <v>490</v>
+      </c>
+      <c r="H272" s="16">
+        <f t="shared" si="9"/>
+        <v>0.15597631000000001</v>
+      </c>
+      <c r="I272" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C273" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273" s="12">
+        <v>60</v>
+      </c>
+      <c r="E273" s="14">
+        <v>10</v>
+      </c>
+      <c r="F273" s="15">
+        <v>1</v>
+      </c>
+      <c r="G273" s="14">
+        <v>550</v>
+      </c>
+      <c r="H273" s="16">
+        <f t="shared" si="9"/>
+        <v>0.17507545000000002</v>
+      </c>
+      <c r="I273" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D274" s="6">
+        <v>60</v>
+      </c>
+      <c r="E274" s="8">
+        <v>0</v>
+      </c>
+      <c r="F274" s="9">
+        <v>0</v>
+      </c>
+      <c r="G274" s="8">
+        <v>10</v>
+      </c>
+      <c r="H274" s="10">
+        <f t="shared" si="9"/>
+        <v>3.1831900000000002E-3</v>
+      </c>
+      <c r="I274" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C275" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D275" s="6">
+        <v>60</v>
+      </c>
+      <c r="E275" s="8">
+        <v>1</v>
+      </c>
+      <c r="F275" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="G275" s="8">
+        <v>30</v>
+      </c>
+      <c r="H275" s="10">
+        <f t="shared" si="9"/>
+        <v>9.5495700000000003E-3</v>
+      </c>
+      <c r="I275" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C276" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D276" s="6">
+        <v>60</v>
+      </c>
+      <c r="E276" s="8">
+        <v>2</v>
+      </c>
+      <c r="F276" s="9">
+        <v>0.31</v>
+      </c>
+      <c r="G276" s="8">
+        <v>110</v>
+      </c>
+      <c r="H276" s="10">
+        <f t="shared" si="9"/>
+        <v>3.5015090000000006E-2</v>
+      </c>
+      <c r="I276" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C277" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D277" s="6">
+        <v>60</v>
+      </c>
+      <c r="E277" s="8">
+        <v>3</v>
+      </c>
+      <c r="F277" s="9">
+        <v>0.46</v>
+      </c>
+      <c r="G277" s="8">
+        <v>240</v>
+      </c>
+      <c r="H277" s="10">
+        <f t="shared" si="9"/>
+        <v>7.6396560000000002E-2</v>
+      </c>
+      <c r="I277" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C278" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D278" s="6">
+        <v>60</v>
+      </c>
+      <c r="E278" s="8">
+        <v>4</v>
+      </c>
+      <c r="F278" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="G278" s="8">
+        <v>388</v>
+      </c>
+      <c r="H278" s="10">
+        <f t="shared" si="9"/>
+        <v>0.12350777200000002</v>
+      </c>
+      <c r="I278" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C279" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D279" s="6">
+        <v>60</v>
+      </c>
+      <c r="E279" s="8">
+        <v>5</v>
+      </c>
+      <c r="F279" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="G279" s="8">
+        <v>530</v>
+      </c>
+      <c r="H279" s="10">
+        <f t="shared" si="9"/>
+        <v>0.16870907000000002</v>
+      </c>
+      <c r="I279" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C280" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D280" s="6">
+        <v>60</v>
+      </c>
+      <c r="E280" s="8">
+        <v>7</v>
+      </c>
+      <c r="F280" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="G280" s="8">
+        <v>690</v>
+      </c>
+      <c r="H280" s="10">
+        <f t="shared" si="9"/>
+        <v>0.21964011</v>
+      </c>
+      <c r="I280" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D281" s="6">
+        <v>60</v>
+      </c>
+      <c r="E281" s="8">
+        <v>10</v>
+      </c>
+      <c r="F281" s="9">
+        <v>1</v>
+      </c>
+      <c r="G281" s="8">
+        <v>761</v>
+      </c>
+      <c r="H281" s="10">
+        <f t="shared" si="9"/>
+        <v>0.24224075900000003</v>
+      </c>
+      <c r="I281" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C282" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D282" s="31">
+        <v>60</v>
+      </c>
+      <c r="E282" s="33">
+        <v>0</v>
+      </c>
+      <c r="F282" s="34">
+        <v>0</v>
+      </c>
+      <c r="G282" s="33">
+        <v>19</v>
+      </c>
+      <c r="H282" s="35">
+        <f t="shared" si="9"/>
+        <v>6.0480610000000004E-3</v>
+      </c>
+      <c r="I282" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B283" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C283" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D283" s="31">
+        <v>60</v>
+      </c>
+      <c r="E283" s="33">
+        <v>1</v>
+      </c>
+      <c r="F283" s="34">
+        <v>0.16</v>
+      </c>
+      <c r="G283" s="33">
+        <v>48</v>
+      </c>
+      <c r="H283" s="35">
+        <f t="shared" si="9"/>
+        <v>1.5279312000000001E-2</v>
+      </c>
+      <c r="I283" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B284" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C284" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D284" s="31">
+        <v>60</v>
+      </c>
+      <c r="E284" s="33">
+        <v>2</v>
+      </c>
+      <c r="F284" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="G284" s="33">
+        <v>109</v>
+      </c>
+      <c r="H284" s="35">
+        <f t="shared" si="9"/>
+        <v>3.4696771000000001E-2</v>
+      </c>
+      <c r="I284" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B285" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C285" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" s="31">
+        <v>60</v>
+      </c>
+      <c r="E285" s="33">
+        <v>3</v>
+      </c>
+      <c r="F285" s="34">
+        <v>0.44</v>
+      </c>
+      <c r="G285" s="33">
+        <v>159</v>
+      </c>
+      <c r="H285" s="35">
+        <f t="shared" si="9"/>
+        <v>5.0612721000000006E-2</v>
+      </c>
+      <c r="I285" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B286" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C286" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286" s="31">
+        <v>60</v>
+      </c>
+      <c r="E286" s="33">
+        <v>4</v>
+      </c>
+      <c r="F286" s="34">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G286" s="33">
+        <v>218</v>
+      </c>
+      <c r="H286" s="35">
+        <f t="shared" si="9"/>
+        <v>6.9393542000000003E-2</v>
+      </c>
+      <c r="I286" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B287" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C287" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D287" s="31">
+        <v>60</v>
+      </c>
+      <c r="E287" s="33">
+        <v>5</v>
+      </c>
+      <c r="F287" s="34">
+        <v>0.71</v>
+      </c>
+      <c r="G287" s="33">
+        <v>297</v>
+      </c>
+      <c r="H287" s="35">
+        <f t="shared" si="9"/>
+        <v>9.4540742999999997E-2</v>
+      </c>
+      <c r="I287" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C288" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D288" s="31">
+        <v>60</v>
+      </c>
+      <c r="E288" s="33">
+        <v>7</v>
+      </c>
+      <c r="F288" s="34">
+        <v>0.87</v>
+      </c>
+      <c r="G288" s="33">
+        <v>379</v>
+      </c>
+      <c r="H288" s="35">
+        <f t="shared" si="9"/>
+        <v>0.12064290100000001</v>
+      </c>
+      <c r="I288" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B289" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C289" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D289" s="31">
+        <v>60</v>
+      </c>
+      <c r="E289" s="33">
+        <v>10</v>
+      </c>
+      <c r="F289" s="34">
+        <v>0.99</v>
+      </c>
+      <c r="G289" s="33">
+        <v>429</v>
+      </c>
+      <c r="H289" s="35">
+        <f t="shared" si="9"/>
+        <v>0.13655885100000001</v>
+      </c>
+      <c r="I289" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="40"/>
+      <c r="B290" s="41"/>
+      <c r="C290" s="40"/>
+      <c r="D290" s="42"/>
+      <c r="E290" s="40"/>
+      <c r="F290" s="43"/>
+      <c r="G290" s="40"/>
+      <c r="H290" s="44"/>
+      <c r="I290" s="45"/>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="40"/>
+      <c r="B291" s="41"/>
+      <c r="C291" s="40"/>
+      <c r="D291" s="42"/>
+      <c r="E291" s="40"/>
+      <c r="F291" s="43"/>
+      <c r="G291" s="40"/>
+      <c r="H291" s="44"/>
+      <c r="I291" s="45"/>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="40"/>
+      <c r="B292" s="41"/>
+      <c r="C292" s="40"/>
+      <c r="D292" s="42"/>
+      <c r="E292" s="40"/>
+      <c r="F292" s="43"/>
+      <c r="G292" s="40"/>
+      <c r="H292" s="44"/>
+      <c r="I292" s="45"/>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="40"/>
+      <c r="B293" s="41"/>
+      <c r="C293" s="40"/>
+      <c r="D293" s="42"/>
+      <c r="E293" s="40"/>
+      <c r="F293" s="43"/>
+      <c r="G293" s="40"/>
+      <c r="H293" s="44"/>
+      <c r="I293" s="45"/>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="40"/>
+      <c r="B294" s="41"/>
+      <c r="C294" s="40"/>
+      <c r="D294" s="42"/>
+      <c r="E294" s="40"/>
+      <c r="F294" s="43"/>
+      <c r="G294" s="40"/>
+      <c r="H294" s="44"/>
+      <c r="I294" s="45"/>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="40"/>
+      <c r="B295" s="41"/>
+      <c r="C295" s="40"/>
+      <c r="D295" s="42"/>
+      <c r="E295" s="40"/>
+      <c r="F295" s="43"/>
+      <c r="G295" s="40"/>
+      <c r="H295" s="44"/>
+      <c r="I295" s="45"/>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="40"/>
+      <c r="B296" s="41"/>
+      <c r="C296" s="40"/>
+      <c r="D296" s="42"/>
+      <c r="E296" s="40"/>
+      <c r="F296" s="43"/>
+      <c r="G296" s="40"/>
+      <c r="H296" s="44"/>
+      <c r="I296" s="45"/>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="40"/>
+      <c r="B297" s="41"/>
+      <c r="C297" s="40"/>
+      <c r="D297" s="42"/>
+      <c r="E297" s="40"/>
+      <c r="F297" s="43"/>
+      <c r="G297" s="40"/>
+      <c r="H297" s="44"/>
+      <c r="I297" s="45"/>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="46"/>
+      <c r="B298" s="47"/>
+      <c r="C298" s="48"/>
+      <c r="D298" s="46"/>
+      <c r="E298" s="48"/>
+      <c r="F298" s="49"/>
+      <c r="G298" s="48"/>
+      <c r="H298" s="50"/>
+      <c r="I298" s="51"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="46"/>
+      <c r="B299" s="47"/>
+      <c r="C299" s="48"/>
+      <c r="D299" s="46"/>
+      <c r="E299" s="48"/>
+      <c r="F299" s="49"/>
+      <c r="G299" s="48"/>
+      <c r="H299" s="50"/>
+      <c r="I299" s="51"/>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="46"/>
+      <c r="B300" s="47"/>
+      <c r="C300" s="48"/>
+      <c r="D300" s="46"/>
+      <c r="E300" s="48"/>
+      <c r="F300" s="49"/>
+      <c r="G300" s="48"/>
+      <c r="H300" s="50"/>
+      <c r="I300" s="51"/>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="46"/>
+      <c r="B301" s="47"/>
+      <c r="C301" s="48"/>
+      <c r="D301" s="46"/>
+      <c r="E301" s="48"/>
+      <c r="F301" s="49"/>
+      <c r="G301" s="48"/>
+      <c r="H301" s="50"/>
+      <c r="I301" s="51"/>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="46"/>
+      <c r="B302" s="47"/>
+      <c r="C302" s="48"/>
+      <c r="D302" s="46"/>
+      <c r="E302" s="48"/>
+      <c r="F302" s="49"/>
+      <c r="G302" s="48"/>
+      <c r="H302" s="50"/>
+      <c r="I302" s="51"/>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="46"/>
+      <c r="B303" s="47"/>
+      <c r="C303" s="48"/>
+      <c r="D303" s="46"/>
+      <c r="E303" s="48"/>
+      <c r="F303" s="49"/>
+      <c r="G303" s="48"/>
+      <c r="H303" s="50"/>
+      <c r="I303" s="51"/>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="46"/>
+      <c r="B304" s="47"/>
+      <c r="C304" s="48"/>
+      <c r="D304" s="46"/>
+      <c r="E304" s="48"/>
+      <c r="F304" s="49"/>
+      <c r="G304" s="48"/>
+      <c r="H304" s="50"/>
+      <c r="I304" s="51"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="46"/>
+      <c r="B305" s="47"/>
+      <c r="C305" s="48"/>
+      <c r="D305" s="46"/>
+      <c r="E305" s="48"/>
+      <c r="F305" s="49"/>
+      <c r="G305" s="48"/>
+      <c r="H305" s="50"/>
+      <c r="I305" s="51"/>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="52"/>
+      <c r="B306" s="52"/>
+      <c r="C306" s="52"/>
+      <c r="D306" s="52"/>
+      <c r="E306" s="52"/>
+      <c r="F306" s="53"/>
+      <c r="G306" s="52"/>
+      <c r="H306" s="54"/>
+      <c r="I306" s="52"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -6744,7 +10169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C117E7FB-486F-48B6-8752-BC50C1B73335}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6755,18 +10180,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F252649E-4352-49A5-A081-F3BFF4884345}">
   <dimension ref="A1:C145"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.625" customWidth="1"/>
-    <col min="2" max="2" width="48.375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>60</v>
       </c>
@@ -6775,7 +10200,7 @@
       </c>
       <c r="C2" s="37"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
         <v>15</v>
       </c>
@@ -6784,7 +10209,7 @@
       </c>
       <c r="C3" s="37"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>56</v>
       </c>
@@ -6792,31 +10217,31 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="39" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>61</v>
       </c>
@@ -6824,7 +10249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
         <v>62</v>
       </c>
@@ -6832,7 +10257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>63</v>
       </c>
@@ -6840,7 +10265,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>64</v>
       </c>
@@ -6848,7 +10273,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
         <v>73</v>
       </c>
@@ -6856,7 +10281,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
         <v>76</v>
       </c>
@@ -6864,15 +10289,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="39" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
         <v>82</v>
       </c>
@@ -6880,7 +10305,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
         <v>87</v>
       </c>
@@ -6888,7 +10313,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
         <v>83</v>
       </c>
@@ -6896,7 +10321,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
         <v>84</v>
       </c>
@@ -6904,511 +10329,563 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="37"/>
-      <c r="B29" s="37"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-      <c r="B30" s="37"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="37"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
       <c r="B32" s="37"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37"/>
       <c r="B33" s="37"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="37"/>
       <c r="B34" s="37"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37"/>
       <c r="B35" s="37"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="37"/>
       <c r="B36" s="37"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="37"/>
       <c r="B37" s="37"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="37"/>
       <c r="B38" s="37"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="37"/>
       <c r="B39" s="37"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="37"/>
       <c r="B40" s="37"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
       <c r="B41" s="37"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
       <c r="B42" s="37"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="37"/>
       <c r="B43" s="37"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="37"/>
       <c r="B44" s="37"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="37"/>
       <c r="B45" s="37"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="37"/>
       <c r="B46" s="37"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="37"/>
       <c r="B47" s="37"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="37"/>
       <c r="B48" s="37"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="37"/>
       <c r="B49" s="37"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="37"/>
       <c r="B50" s="37"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="37"/>
       <c r="B51" s="37"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="37"/>
       <c r="B52" s="37"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="37"/>
       <c r="B53" s="37"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="37"/>
       <c r="B54" s="37"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="37"/>
       <c r="B55" s="37"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="37"/>
       <c r="B56" s="37"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="37"/>
       <c r="B57" s="37"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="37"/>
       <c r="B58" s="37"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="37"/>
       <c r="B59" s="37"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="37"/>
       <c r="B60" s="37"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="37"/>
       <c r="B61" s="37"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="37"/>
       <c r="B62" s="37"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="37"/>
       <c r="B63" s="37"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="37"/>
       <c r="B64" s="37"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="37"/>
       <c r="B65" s="37"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="37"/>
       <c r="B66" s="37"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="37"/>
       <c r="B67" s="37"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="37"/>
       <c r="B68" s="37"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="37"/>
       <c r="B69" s="37"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="37"/>
       <c r="B70" s="37"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="37"/>
       <c r="B71" s="37"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="37"/>
       <c r="B72" s="37"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="37"/>
       <c r="B73" s="37"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="37"/>
       <c r="B74" s="37"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="37"/>
       <c r="B75" s="37"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="37"/>
       <c r="B76" s="37"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="37"/>
       <c r="B77" s="37"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="37"/>
       <c r="B78" s="37"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="37"/>
       <c r="B79" s="37"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="37"/>
       <c r="B80" s="37"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="37"/>
       <c r="B81" s="37"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="37"/>
       <c r="B82" s="37"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="37"/>
       <c r="B83" s="37"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="37"/>
       <c r="B84" s="37"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="37"/>
       <c r="B85" s="37"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="37"/>
       <c r="B86" s="37"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="37"/>
       <c r="B87" s="37"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="37"/>
       <c r="B88" s="37"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="37"/>
       <c r="B89" s="37"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="37"/>
       <c r="B90" s="37"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="37"/>
       <c r="B91" s="37"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="37"/>
       <c r="B92" s="37"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="37"/>
       <c r="B93" s="37"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="37"/>
       <c r="B94" s="37"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="37"/>
       <c r="B95" s="37"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="37"/>
       <c r="B96" s="37"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="37"/>
       <c r="B97" s="37"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="37"/>
       <c r="B98" s="37"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="37"/>
       <c r="B99" s="37"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="37"/>
       <c r="B100" s="37"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="37"/>
       <c r="B101" s="37"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="37"/>
       <c r="B102" s="37"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="37"/>
       <c r="B103" s="37"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="37"/>
       <c r="B104" s="37"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="37"/>
       <c r="B105" s="37"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="37"/>
       <c r="B106" s="37"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="37"/>
       <c r="B107" s="37"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="37"/>
       <c r="B108" s="37"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="37"/>
       <c r="B109" s="37"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="37"/>
       <c r="B110" s="37"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="37"/>
       <c r="B111" s="37"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="37"/>
       <c r="B112" s="37"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="37"/>
       <c r="B113" s="37"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="37"/>
       <c r="B114" s="37"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="37"/>
       <c r="B115" s="37"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="37"/>
       <c r="B116" s="37"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="37"/>
       <c r="B117" s="37"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="37"/>
       <c r="B118" s="37"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="37"/>
       <c r="B119" s="37"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="37"/>
       <c r="B120" s="37"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="37"/>
       <c r="B121" s="37"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="37"/>
       <c r="B122" s="37"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="37"/>
       <c r="B123" s="37"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="37"/>
       <c r="B124" s="37"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="37"/>
       <c r="B125" s="37"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="37"/>
       <c r="B126" s="37"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="37"/>
       <c r="B127" s="37"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="37"/>
       <c r="B128" s="37"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="37"/>
       <c r="B129" s="37"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="37"/>
       <c r="B130" s="37"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="37"/>
       <c r="B131" s="37"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="37"/>
       <c r="B132" s="37"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="37"/>
       <c r="B133" s="37"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="37"/>
       <c r="B134" s="37"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="37"/>
       <c r="B135" s="37"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="37"/>
       <c r="B136" s="37"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="37"/>
       <c r="B137" s="37"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="37"/>
       <c r="B138" s="37"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="37"/>
       <c r="B139" s="37"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="37"/>
       <c r="B140" s="37"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="37"/>
       <c r="B141" s="37"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="37"/>
       <c r="B142" s="37"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="37"/>
       <c r="B143" s="37"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="37"/>
       <c r="B144" s="37"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="37"/>
       <c r="B145" s="37"/>
     </row>

--- a/自研流变仪材料测试数据.xlsx
+++ b/自研流变仪材料测试数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yxin\Desktop\0523\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Desktop\博士\huawei\交付流变仪\自研流变仪测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233B88BF-FD17-469D-ACC7-607BE796B370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0A5497-4B8A-4617-8F55-00657DC2A3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,20 +18,29 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Data_Form" localSheetId="0" hidden="1">Sheet1!$A$1:$I$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$67</definedName>
-    <definedName name="_xlnm.Data_Form" localSheetId="0" hidden="1">Sheet1!$A$1:$I$49</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="148">
   <si>
     <t>平行杆</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -263,9 +272,6 @@
     <t>C32</t>
   </si>
   <si>
-    <t>DKN7500-ZY01-STBC-TYY55-92-0.4 6.6 3</t>
-  </si>
-  <si>
     <t>c32</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -512,6 +518,49 @@
   <si>
     <t>DKN10000-QZ08-STBC-TYY55-90-0.4 8.6 1</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN7500-XD05-STBC-XD30-92.7-1 8 1复配</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0525</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN7500-ZY01-STBC-TYY55-92-0.4 6.6 3复配</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C32-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0525</t>
+  </si>
+  <si>
+    <t>c16-2</t>
+  </si>
+  <si>
+    <t>c16-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN5000-ZY01-STBC-TYY55-92-0.4 6.6 3复配</t>
+  </si>
+  <si>
+    <t>DKN5000-ZY01-STBC-TYY55-92-0.4 6.6 3复配</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c53</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DKN7500-ZY01-STBC-TYY55-90-0.4 8.6 1</t>
+  </si>
+  <si>
+    <t>c53</t>
   </si>
 </sst>
 </file>
@@ -629,7 +678,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -706,33 +755,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - 着色 1" xfId="2" builtinId="30"/>
@@ -1287,19 +1309,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I306"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I321"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.88671875" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="39.875" customWidth="1"/>
+    <col min="2" max="2" width="44.5" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="6" max="6" width="9" style="3"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="5" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -1358,7 +1380,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
@@ -1388,7 +1410,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
@@ -1418,7 +1440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1448,7 +1470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1478,7 +1500,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1508,7 +1530,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
@@ -1538,7 +1560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
         <v>15</v>
       </c>
@@ -1568,7 +1590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
         <v>15</v>
       </c>
@@ -1598,7 +1620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>15</v>
       </c>
@@ -1628,7 +1650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
@@ -1658,7 +1680,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>15</v>
       </c>
@@ -1688,7 +1710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>14</v>
       </c>
@@ -1718,7 +1740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
@@ -1748,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -1778,7 +1800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -1808,7 +1830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>15</v>
       </c>
@@ -1838,7 +1860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>15</v>
       </c>
@@ -1868,7 +1890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="31" t="s">
         <v>20</v>
       </c>
@@ -1898,7 +1920,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
@@ -1928,7 +1950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="31" t="s">
         <v>20</v>
       </c>
@@ -1958,7 +1980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
         <v>20</v>
       </c>
@@ -1988,7 +2010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="31" t="s">
         <v>20</v>
       </c>
@@ -2018,7 +2040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="31" t="s">
         <v>20</v>
       </c>
@@ -2048,7 +2070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>20</v>
       </c>
@@ -2078,7 +2100,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
@@ -2108,7 +2130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -2138,7 +2160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -2168,7 +2190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>20</v>
       </c>
@@ -2198,7 +2220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -2228,7 +2250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
         <v>44</v>
       </c>
@@ -2258,7 +2280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
         <v>44</v>
       </c>
@@ -2288,7 +2310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
         <v>44</v>
       </c>
@@ -2318,7 +2340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
         <v>44</v>
       </c>
@@ -2348,7 +2370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
         <v>44</v>
       </c>
@@ -2378,7 +2400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="18" t="s">
         <v>44</v>
       </c>
@@ -2408,7 +2430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="31" t="s">
         <v>15</v>
       </c>
@@ -2438,7 +2460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="31" t="s">
         <v>15</v>
       </c>
@@ -2468,7 +2490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>15</v>
       </c>
@@ -2498,7 +2520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>15</v>
       </c>
@@ -2528,7 +2550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>15</v>
       </c>
@@ -2558,7 +2580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>15</v>
       </c>
@@ -2588,7 +2610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>45</v>
       </c>
@@ -2618,7 +2640,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
@@ -2648,7 +2670,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>45</v>
       </c>
@@ -2678,7 +2700,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>45</v>
       </c>
@@ -2708,7 +2730,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>45</v>
       </c>
@@ -2738,7 +2760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>45</v>
       </c>
@@ -2768,7 +2790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>46</v>
       </c>
@@ -2798,7 +2820,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>46</v>
       </c>
@@ -2828,7 +2850,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -2858,7 +2880,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>46</v>
       </c>
@@ -2888,7 +2910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>46</v>
       </c>
@@ -2918,7 +2940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>46</v>
       </c>
@@ -2948,7 +2970,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>20</v>
       </c>
@@ -2978,7 +3000,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>20</v>
       </c>
@@ -3008,7 +3030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>20</v>
       </c>
@@ -3038,7 +3060,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>20</v>
       </c>
@@ -3068,7 +3090,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>20</v>
       </c>
@@ -3098,7 +3120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>20</v>
       </c>
@@ -3128,7 +3150,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -3158,7 +3180,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>43</v>
       </c>
@@ -3188,7 +3210,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>43</v>
       </c>
@@ -3218,7 +3240,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>43</v>
       </c>
@@ -3248,7 +3270,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>43</v>
       </c>
@@ -3278,7 +3300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>43</v>
       </c>
@@ -3308,9 +3330,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>47</v>
@@ -3338,9 +3360,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>47</v>
@@ -3368,9 +3390,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>47</v>
@@ -3398,9 +3420,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>49</v>
@@ -3428,9 +3450,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>47</v>
@@ -3458,9 +3480,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>47</v>
@@ -3488,9 +3510,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>47</v>
@@ -3518,9 +3540,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>47</v>
@@ -3548,9 +3570,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>50</v>
@@ -3578,9 +3600,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>50</v>
@@ -3608,9 +3630,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>50</v>
@@ -3638,9 +3660,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>50</v>
@@ -3668,9 +3690,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>50</v>
@@ -3698,9 +3720,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>50</v>
@@ -3728,9 +3750,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>50</v>
@@ -3758,9 +3780,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>50</v>
@@ -3788,9 +3810,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B84" s="30" t="s">
         <v>52</v>
@@ -3818,9 +3840,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B85" s="30" t="s">
         <v>52</v>
@@ -3848,9 +3870,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B86" s="30" t="s">
         <v>52</v>
@@ -3878,9 +3900,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B87" s="30" t="s">
         <v>52</v>
@@ -3908,9 +3930,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B88" s="30" t="s">
         <v>52</v>
@@ -3938,9 +3960,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B89" s="30" t="s">
         <v>52</v>
@@ -3968,9 +3990,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B90" s="30" t="s">
         <v>52</v>
@@ -3998,9 +4020,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B91" s="30" t="s">
         <v>52</v>
@@ -4028,9 +4050,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92" s="32" t="s">
         <v>55</v>
@@ -4058,9 +4080,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B93" s="32" t="s">
         <v>55</v>
@@ -4088,9 +4110,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B94" s="32" t="s">
         <v>55</v>
@@ -4118,9 +4140,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B95" s="32" t="s">
         <v>55</v>
@@ -4148,9 +4170,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B96" s="32" t="s">
         <v>55</v>
@@ -4178,9 +4200,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>55</v>
@@ -4208,9 +4230,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B98" s="32" t="s">
         <v>55</v>
@@ -4238,9 +4260,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B99" s="32" t="s">
         <v>55</v>
@@ -4268,7 +4290,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
         <v>20</v>
       </c>
@@ -4298,7 +4320,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
         <v>20</v>
       </c>
@@ -4328,7 +4350,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
         <v>20</v>
       </c>
@@ -4358,7 +4380,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
         <v>20</v>
       </c>
@@ -4388,7 +4410,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
         <v>20</v>
       </c>
@@ -4418,7 +4440,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
         <v>20</v>
       </c>
@@ -4448,7 +4470,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
         <v>20</v>
       </c>
@@ -4478,7 +4500,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
         <v>20</v>
       </c>
@@ -4508,9 +4530,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>55</v>
@@ -4538,9 +4560,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B109" s="32" t="s">
         <v>55</v>
@@ -4568,9 +4590,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B110" s="32" t="s">
         <v>55</v>
@@ -4598,9 +4620,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>55</v>
@@ -4628,9 +4650,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B112" s="32" t="s">
         <v>55</v>
@@ -4658,9 +4680,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B113" s="32" t="s">
         <v>55</v>
@@ -4688,9 +4710,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>55</v>
@@ -4718,9 +4740,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B115" s="32" t="s">
         <v>55</v>
@@ -4748,7 +4770,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="12" t="s">
         <v>46</v>
       </c>
@@ -4775,10 +4797,10 @@
         <v>4.7111212E-2</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="12" t="s">
         <v>46</v>
       </c>
@@ -4805,10 +4827,10 @@
         <v>5.6979101000000004E-2</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="12" t="s">
         <v>46</v>
       </c>
@@ -4835,10 +4857,10 @@
         <v>8.4672854000000006E-2</v>
       </c>
       <c r="I118" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="12" t="s">
         <v>46</v>
       </c>
@@ -4865,10 +4887,10 @@
         <v>0.12605432400000002</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="12" t="s">
         <v>46</v>
       </c>
@@ -4895,10 +4917,10 @@
         <v>0.158204543</v>
       </c>
       <c r="I120" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="12" t="s">
         <v>46</v>
       </c>
@@ -4925,10 +4947,10 @@
         <v>0.19290131400000002</v>
       </c>
       <c r="I121" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="12" t="s">
         <v>46</v>
       </c>
@@ -4955,10 +4977,10 @@
         <v>0.23587437900000002</v>
       </c>
       <c r="I122" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="12" t="s">
         <v>46</v>
       </c>
@@ -4985,10 +5007,10 @@
         <v>0.26706964100000002</v>
       </c>
       <c r="I123" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
         <v>45</v>
       </c>
@@ -5015,10 +5037,10 @@
         <v>3.9789875000000002E-2</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
         <v>45</v>
       </c>
@@ -5045,10 +5067,10 @@
         <v>9.008427699999999E-2</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
         <v>45</v>
       </c>
@@ -5075,10 +5097,10 @@
         <v>0.12287113400000001</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
         <v>45</v>
       </c>
@@ -5105,10 +5127,10 @@
         <v>0.155021353</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
         <v>45</v>
       </c>
@@ -5135,10 +5157,10 @@
         <v>0.185261658</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
         <v>45</v>
       </c>
@@ -5165,10 +5187,10 @@
         <v>0.20849894500000002</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
         <v>45</v>
       </c>
@@ -5195,10 +5217,10 @@
         <v>0.236829336</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
         <v>45</v>
       </c>
@@ -5225,15 +5247,15 @@
         <v>0.25529183800000005</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C132" s="20" t="s">
         <v>9</v>
@@ -5255,15 +5277,15 @@
         <v>4.7747850000000001E-3</v>
       </c>
       <c r="I132" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C133" s="20" t="s">
         <v>9</v>
@@ -5285,15 +5307,15 @@
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I133" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C134" s="20" t="s">
         <v>9</v>
@@ -5315,15 +5337,15 @@
         <v>5.6660782E-2</v>
       </c>
       <c r="I134" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C135" s="20" t="s">
         <v>9</v>
@@ -5345,15 +5367,15 @@
         <v>8.3081259000000005E-2</v>
       </c>
       <c r="I135" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C136" s="20" t="s">
         <v>9</v>
@@ -5375,15 +5397,15 @@
         <v>0.111729969</v>
       </c>
       <c r="I136" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C137" s="20" t="s">
         <v>19</v>
@@ -5405,15 +5427,15 @@
         <v>0.14547178300000002</v>
       </c>
       <c r="I137" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C138" s="20" t="s">
         <v>19</v>
@@ -5435,15 +5457,15 @@
         <v>0.19353795200000001</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C139" s="20" t="s">
         <v>19</v>
@@ -5465,15 +5487,15 @@
         <v>0.23555606000000001</v>
       </c>
       <c r="I139" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B140" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B140" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C140" s="33" t="s">
         <v>9</v>
@@ -5495,15 +5517,15 @@
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B141" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B141" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C141" s="33" t="s">
         <v>9</v>
@@ -5525,15 +5547,15 @@
         <v>2.8012071999999999E-2</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B142" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B142" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C142" s="33" t="s">
         <v>9</v>
@@ -5555,15 +5577,15 @@
         <v>4.2654746000000007E-2</v>
       </c>
       <c r="I142" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B143" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B143" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C143" s="33" t="s">
         <v>9</v>
@@ -5585,15 +5607,15 @@
         <v>7.1621775000000013E-2</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B144" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B144" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>9</v>
@@ -5615,15 +5637,15 @@
         <v>0.10154376100000001</v>
       </c>
       <c r="I144" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B145" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B145" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>19</v>
@@ -5645,15 +5667,15 @@
         <v>0.14197027400000001</v>
       </c>
       <c r="I145" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B146" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B146" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>19</v>
@@ -5675,15 +5697,15 @@
         <v>0.20627071200000002</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B147" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="B147" s="32" t="s">
-        <v>77</v>
       </c>
       <c r="C147" s="33" t="s">
         <v>19</v>
@@ -5705,15 +5727,15 @@
         <v>0.22536985200000001</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>9</v>
@@ -5735,15 +5757,15 @@
         <v>-8.276294E-3</v>
       </c>
       <c r="I148" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>9</v>
@@ -5765,15 +5787,15 @@
         <v>3.1831900000000002E-3</v>
       </c>
       <c r="I149" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>9</v>
@@ -5795,15 +5817,15 @@
         <v>2.1964011000000002E-2</v>
       </c>
       <c r="I150" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C151" s="14" t="s">
         <v>9</v>
@@ -5825,15 +5847,15 @@
         <v>7.5123283999999999E-2</v>
       </c>
       <c r="I151" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C152" s="14" t="s">
         <v>9</v>
@@ -5855,15 +5877,15 @@
         <v>0.125417686</v>
       </c>
       <c r="I152" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C153" s="14" t="s">
         <v>19</v>
@@ -5885,15 +5907,15 @@
         <v>0.20531575500000002</v>
       </c>
       <c r="I153" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C154" s="14" t="s">
         <v>19</v>
@@ -5915,15 +5937,15 @@
         <v>0.26675132200000001</v>
       </c>
       <c r="I154" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C155" s="14" t="s">
         <v>19</v>
@@ -5945,15 +5967,15 @@
         <v>0.31704572400000003</v>
       </c>
       <c r="I155" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>9</v>
@@ -5975,15 +5997,15 @@
         <v>2.1645692000000001E-2</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>9</v>
@@ -6005,15 +6027,15 @@
         <v>2.8012071999999999E-2</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>9</v>
@@ -6035,15 +6057,15 @@
         <v>4.9339445000000003E-2</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>9</v>
@@ -6065,15 +6087,15 @@
         <v>8.244462100000001E-2</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>9</v>
@@ -6095,15 +6117,15 @@
         <v>0.12223449600000001</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>9</v>
@@ -6125,15 +6147,15 @@
         <v>0.16075109500000001</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>9</v>
@@ -6155,15 +6177,15 @@
         <v>0.22536985200000001</v>
       </c>
       <c r="I162" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>9</v>
@@ -6185,15 +6207,15 @@
         <v>0.282030634</v>
       </c>
       <c r="I163" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B164" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B164" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C164" s="33" t="s">
         <v>9</v>
@@ -6215,15 +6237,15 @@
         <v>-1.0504527000000001E-2</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B165" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B165" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C165" s="33" t="s">
         <v>9</v>
@@ -6245,15 +6267,15 @@
         <v>-6.3663800000000003E-4</v>
       </c>
       <c r="I165" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B166" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B166" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C166" s="33" t="s">
         <v>9</v>
@@ -6275,15 +6297,15 @@
         <v>8.276294E-3</v>
       </c>
       <c r="I166" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B167" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B167" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C167" s="33" t="s">
         <v>9</v>
@@ -6305,15 +6327,15 @@
         <v>2.7375434000000001E-2</v>
       </c>
       <c r="I167" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B168" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B168" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C168" s="33" t="s">
         <v>9</v>
@@ -6335,15 +6357,15 @@
         <v>5.9843972000000002E-2</v>
       </c>
       <c r="I168" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B169" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B169" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C169" s="33" t="s">
         <v>19</v>
@@ -6365,15 +6387,15 @@
         <v>7.894311200000001E-2</v>
       </c>
       <c r="I169" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B170" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B170" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C170" s="33" t="s">
         <v>19</v>
@@ -6395,15 +6417,15 @@
         <v>0.12032458200000001</v>
       </c>
       <c r="I170" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B171" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="B171" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="C171" s="33" t="s">
         <v>19</v>
@@ -6425,15 +6447,15 @@
         <v>0.145790102</v>
       </c>
       <c r="I171" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C172" s="20" t="s">
         <v>9</v>
@@ -6455,15 +6477,15 @@
         <v>-1.4006035999999999E-2</v>
       </c>
       <c r="I172" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B173" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C173" s="20" t="s">
         <v>9</v>
@@ -6485,15 +6507,15 @@
         <v>-1.0186208E-2</v>
       </c>
       <c r="I173" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B174" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C174" s="20" t="s">
         <v>9</v>
@@ -6515,15 +6537,15 @@
         <v>1.7825864E-2</v>
       </c>
       <c r="I174" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B175" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C175" s="20" t="s">
         <v>9</v>
@@ -6545,15 +6567,15 @@
         <v>3.7243323000000002E-2</v>
       </c>
       <c r="I175" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B176" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C176" s="20" t="s">
         <v>9</v>
@@ -6575,15 +6597,15 @@
         <v>6.8756904000000008E-2</v>
       </c>
       <c r="I176" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C177" s="20" t="s">
         <v>19</v>
@@ -6605,15 +6627,15 @@
         <v>0.104090313</v>
       </c>
       <c r="I177" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C178" s="20" t="s">
         <v>19</v>
@@ -6635,15 +6657,15 @@
         <v>0.14228859300000002</v>
       </c>
       <c r="I178" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C179" s="20" t="s">
         <v>19</v>
@@ -6665,15 +6687,15 @@
         <v>0.193856271</v>
       </c>
       <c r="I179" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>9</v>
@@ -6695,15 +6717,15 @@
         <v>-6.3663800000000003E-4</v>
       </c>
       <c r="I180" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>9</v>
@@ -6725,15 +6747,15 @@
         <v>5.4114230000000003E-3</v>
       </c>
       <c r="I181" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>9</v>
@@ -6755,15 +6777,15 @@
         <v>2.7375434000000001E-2</v>
       </c>
       <c r="I182" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>9</v>
@@ -6785,15 +6807,15 @@
         <v>6.8756904000000008E-2</v>
       </c>
       <c r="I183" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>9</v>
@@ -6815,15 +6837,15 @@
         <v>0.10727350300000002</v>
       </c>
       <c r="I184" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C185" s="14" t="s">
         <v>9</v>
@@ -6845,15 +6867,15 @@
         <v>0.15533967200000001</v>
       </c>
       <c r="I185" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>9</v>
@@ -6875,15 +6897,15 @@
         <v>0.21231877300000002</v>
       </c>
       <c r="I186" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>9</v>
@@ -6905,15 +6927,15 @@
         <v>0.26388645100000002</v>
       </c>
       <c r="I187" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A188" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B188" s="7" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>9</v>
@@ -6935,15 +6957,15 @@
         <v>5.7297419999999995E-3</v>
       </c>
       <c r="I188" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>9</v>
@@ -6965,15 +6987,15 @@
         <v>1.0822846000000001E-2</v>
       </c>
       <c r="I189" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>9</v>
@@ -6995,15 +7017,15 @@
         <v>2.4828882E-2</v>
       </c>
       <c r="I190" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>9</v>
@@ -7025,15 +7047,15 @@
         <v>7.894311200000001E-2</v>
       </c>
       <c r="I191" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>9</v>
@@ -7055,15 +7077,15 @@
         <v>0.123189453</v>
       </c>
       <c r="I192" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>9</v>
@@ -7085,15 +7107,15 @@
         <v>0.17093730300000001</v>
       </c>
       <c r="I193" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>9</v>
@@ -7115,15 +7137,15 @@
         <v>0.21645692000000002</v>
       </c>
       <c r="I194" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>9</v>
@@ -7145,15 +7167,15 @@
         <v>0.28298559100000004</v>
       </c>
       <c r="I195" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A196" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B196" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C196" s="33" t="s">
         <v>9</v>
@@ -7175,15 +7197,15 @@
         <v>5.7297419999999995E-3</v>
       </c>
       <c r="I196" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A197" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B197" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C197" s="33" t="s">
         <v>9</v>
@@ -7205,15 +7227,15 @@
         <v>2.4828882E-2</v>
       </c>
       <c r="I197" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A198" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B198" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C198" s="33" t="s">
         <v>9</v>
@@ -7235,15 +7257,15 @@
         <v>4.0744832000000002E-2</v>
       </c>
       <c r="I198" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A199" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B199" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C199" s="33" t="s">
         <v>9</v>
@@ -7265,15 +7287,15 @@
         <v>5.9525653000000005E-2</v>
       </c>
       <c r="I199" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A200" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B200" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C200" s="33" t="s">
         <v>9</v>
@@ -7295,15 +7317,15 @@
         <v>7.5759922000000007E-2</v>
       </c>
       <c r="I200" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A201" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B201" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C201" s="33" t="s">
         <v>19</v>
@@ -7325,15 +7347,15 @@
         <v>8.8492682000000017E-2</v>
       </c>
       <c r="I201" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A202" s="33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="33" t="s">
-        <v>98</v>
-      </c>
       <c r="B202" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C202" s="33" t="s">
         <v>19</v>
@@ -7355,15 +7377,15 @@
         <v>0.12955583300000001</v>
       </c>
       <c r="I202" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B203" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C203" s="20" t="s">
         <v>9</v>
@@ -7385,15 +7407,15 @@
         <v>0</v>
       </c>
       <c r="I203" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B204" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C204" s="20" t="s">
         <v>9</v>
@@ -7415,15 +7437,15 @@
         <v>6.3663800000000005E-3</v>
       </c>
       <c r="I204" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B205" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C205" s="20" t="s">
         <v>9</v>
@@ -7445,15 +7467,15 @@
         <v>4.4246341000000008E-2</v>
       </c>
       <c r="I205" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B206" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C206" s="20" t="s">
         <v>9</v>
@@ -7475,15 +7497,15 @@
         <v>0.12669096200000002</v>
       </c>
       <c r="I206" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B207" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C207" s="20" t="s">
         <v>9</v>
@@ -7505,15 +7527,15 @@
         <v>0.18112351099999999</v>
       </c>
       <c r="I207" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B208" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C208" s="20" t="s">
         <v>19</v>
@@ -7535,15 +7557,15 @@
         <v>0.23587437900000002</v>
       </c>
       <c r="I208" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B209" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C209" s="20" t="s">
         <v>19</v>
@@ -7565,15 +7587,15 @@
         <v>0.30240305000000001</v>
       </c>
       <c r="I209" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B210" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C210" s="20" t="s">
         <v>19</v>
@@ -7595,15 +7617,15 @@
         <v>0.353652409</v>
       </c>
       <c r="I210" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>9</v>
@@ -7625,15 +7647,15 @@
         <v>7.9579750000000008E-3</v>
       </c>
       <c r="I211" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>9</v>
@@ -7655,15 +7677,15 @@
         <v>2.4510563000000003E-2</v>
       </c>
       <c r="I212" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>9</v>
@@ -7685,15 +7707,15 @@
         <v>4.9976083000000004E-2</v>
       </c>
       <c r="I213" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C214" s="14" t="s">
         <v>9</v>
@@ -7715,15 +7737,15 @@
         <v>0.10122544200000001</v>
       </c>
       <c r="I214" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C215" s="14" t="s">
         <v>9</v>
@@ -7745,15 +7767,15 @@
         <v>0.136240532</v>
       </c>
       <c r="I215" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>9</v>
@@ -7775,15 +7797,15 @@
         <v>0.17730368300000002</v>
       </c>
       <c r="I216" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>9</v>
@@ -7805,15 +7827,15 @@
         <v>0.24446899200000002</v>
       </c>
       <c r="I217" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>9</v>
@@ -7835,15 +7857,15 @@
         <v>0.26738795999999998</v>
       </c>
       <c r="I218" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>9</v>
@@ -7865,15 +7887,15 @@
         <v>-3.8198280000000004E-3</v>
       </c>
       <c r="I219" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>9</v>
@@ -7895,15 +7917,15 @@
         <v>2.5465520000000001E-3</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C221" s="8" t="s">
         <v>9</v>
@@ -7925,15 +7947,15 @@
         <v>2.1009054000000003E-2</v>
       </c>
       <c r="I221" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C222" s="8" t="s">
         <v>9</v>
@@ -7955,15 +7977,15 @@
         <v>6.8756904000000008E-2</v>
       </c>
       <c r="I222" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C223" s="8" t="s">
         <v>9</v>
@@ -7985,15 +8007,15 @@
         <v>0.12605432400000002</v>
       </c>
       <c r="I223" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C224" s="8" t="s">
         <v>9</v>
@@ -8015,15 +8037,15 @@
         <v>0.16775411300000001</v>
       </c>
       <c r="I224" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C225" s="8" t="s">
         <v>9</v>
@@ -8045,15 +8067,15 @@
         <v>0.19926769400000002</v>
       </c>
       <c r="I225" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C226" s="8" t="s">
         <v>9</v>
@@ -8075,15 +8097,15 @@
         <v>0.23873925000000001</v>
       </c>
       <c r="I226" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B227" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C227" s="33" t="s">
         <v>9</v>
@@ -8105,15 +8127,15 @@
         <v>1.8144183000000001E-2</v>
       </c>
       <c r="I227" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B228" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C228" s="33" t="s">
         <v>9</v>
@@ -8135,15 +8157,15 @@
         <v>7.194009400000001E-2</v>
       </c>
       <c r="I228" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B229" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C229" s="33" t="s">
         <v>9</v>
@@ -8165,15 +8187,15 @@
         <v>0.119687944</v>
       </c>
       <c r="I229" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B230" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C230" s="33" t="s">
         <v>9</v>
@@ -8195,15 +8217,15 @@
         <v>0.151838163</v>
       </c>
       <c r="I230" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B231" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C231" s="33" t="s">
         <v>9</v>
@@ -8225,15 +8247,15 @@
         <v>0.186853253</v>
       </c>
       <c r="I231" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B232" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C232" s="33" t="s">
         <v>19</v>
@@ -8255,15 +8277,15 @@
         <v>0.22918968000000001</v>
       </c>
       <c r="I232" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B233" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C233" s="33" t="s">
         <v>19</v>
@@ -8285,15 +8307,15 @@
         <v>0.28585046200000003</v>
       </c>
       <c r="I233" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B234" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C234" s="33" t="s">
         <v>19</v>
@@ -8315,15 +8337,15 @@
         <v>0.31449917199999999</v>
       </c>
       <c r="I234" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B235" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C235" s="20" t="s">
         <v>9</v>
@@ -8345,15 +8367,15 @@
         <v>5.7297419999999995E-3</v>
       </c>
       <c r="I235" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B236" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C236" s="20" t="s">
         <v>9</v>
@@ -8375,15 +8397,15 @@
         <v>1.1459483999999999E-2</v>
       </c>
       <c r="I236" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B237" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C237" s="20" t="s">
         <v>9</v>
@@ -8405,15 +8427,15 @@
         <v>7.8624792999999998E-2</v>
       </c>
       <c r="I237" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B238" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C238" s="20" t="s">
         <v>9</v>
@@ -8435,15 +8457,15 @@
         <v>0.13878708400000001</v>
       </c>
       <c r="I238" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B239" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C239" s="20" t="s">
         <v>9</v>
@@ -8465,15 +8487,15 @@
         <v>0.21582028200000003</v>
       </c>
       <c r="I239" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B240" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C240" s="20" t="s">
         <v>19</v>
@@ -8495,15 +8517,15 @@
         <v>0.26706964100000002</v>
       </c>
       <c r="I240" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B241" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C241" s="20" t="s">
         <v>19</v>
@@ -8525,15 +8547,15 @@
         <v>0.34696771000000004</v>
       </c>
       <c r="I241" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B242" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C242" s="20" t="s">
         <v>19</v>
@@ -8555,15 +8577,15 @@
         <v>0.40426513000000003</v>
       </c>
       <c r="I242" s="23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C243" s="14" t="s">
         <v>9</v>
@@ -8585,15 +8607,15 @@
         <v>0</v>
       </c>
       <c r="I243" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C244" s="14" t="s">
         <v>9</v>
@@ -8615,15 +8637,15 @@
         <v>5.7297419999999995E-3</v>
       </c>
       <c r="I244" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B245" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C245" s="14" t="s">
         <v>9</v>
@@ -8645,15 +8667,15 @@
         <v>2.7693752999999998E-2</v>
       </c>
       <c r="I245" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C246" s="14" t="s">
         <v>9</v>
@@ -8675,15 +8697,15 @@
         <v>4.6474573999999998E-2</v>
       </c>
       <c r="I246" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B247" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C247" s="14" t="s">
         <v>9</v>
@@ -8705,15 +8727,15 @@
         <v>7.5441602999999996E-2</v>
       </c>
       <c r="I247" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C248" s="14" t="s">
         <v>9</v>
@@ -8735,15 +8757,15 @@
         <v>0.10727350300000002</v>
       </c>
       <c r="I248" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C249" s="14" t="s">
         <v>9</v>
@@ -8765,15 +8787,15 @@
         <v>0.14547178300000002</v>
       </c>
       <c r="I249" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C250" s="14" t="s">
         <v>9</v>
@@ -8795,15 +8817,15 @@
         <v>0.16743579400000003</v>
       </c>
       <c r="I250" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C251" s="8" t="s">
         <v>9</v>
@@ -8825,15 +8847,15 @@
         <v>5.4114230000000003E-3</v>
       </c>
       <c r="I251" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C252" s="8" t="s">
         <v>9</v>
@@ -8855,15 +8877,15 @@
         <v>3.4060132999999999E-2</v>
       </c>
       <c r="I252" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C253" s="8" t="s">
         <v>9</v>
@@ -8885,15 +8907,15 @@
         <v>5.9525653000000005E-2</v>
       </c>
       <c r="I253" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>9</v>
@@ -8915,15 +8937,15 @@
         <v>8.4672854000000006E-2</v>
       </c>
       <c r="I254" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C255" s="8" t="s">
         <v>9</v>
@@ -8945,15 +8967,15 @@
         <v>0.116823073</v>
       </c>
       <c r="I255" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>9</v>
@@ -8975,15 +8997,15 @@
         <v>0.15247480099999999</v>
       </c>
       <c r="I256" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C257" s="8" t="s">
         <v>9</v>
@@ -9005,15 +9027,15 @@
         <v>0.16775411300000001</v>
       </c>
       <c r="I257" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B258" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C258" s="33" t="s">
         <v>9</v>
@@ -9031,19 +9053,19 @@
         <v>8</v>
       </c>
       <c r="H258" s="35">
-        <f t="shared" ref="H258:H289" si="9">G258/1000*0.318319</f>
+        <f t="shared" ref="H258:H297" si="9">G258/1000*0.318319</f>
         <v>2.5465520000000001E-3</v>
       </c>
       <c r="I258" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B259" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C259" s="33" t="s">
         <v>9</v>
@@ -9065,15 +9087,15 @@
         <v>6.3663800000000005E-3</v>
       </c>
       <c r="I259" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B260" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C260" s="33" t="s">
         <v>9</v>
@@ -9095,15 +9117,15 @@
         <v>3.4378452000000004E-2</v>
       </c>
       <c r="I260" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B261" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C261" s="33" t="s">
         <v>9</v>
@@ -9125,15 +9147,15 @@
         <v>6.6528670999999998E-2</v>
       </c>
       <c r="I261" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B262" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C262" s="33" t="s">
         <v>9</v>
@@ -9155,15 +9177,15 @@
         <v>0.100588804</v>
       </c>
       <c r="I262" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B263" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C263" s="33" t="s">
         <v>19</v>
@@ -9185,15 +9207,15 @@
         <v>0.142606912</v>
       </c>
       <c r="I263" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B264" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C264" s="33" t="s">
         <v>19</v>
@@ -9215,15 +9237,15 @@
         <v>0.17794032100000004</v>
       </c>
       <c r="I264" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B265" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C265" s="33" t="s">
         <v>19</v>
@@ -9245,15 +9267,15 @@
         <v>0.20117760800000001</v>
       </c>
       <c r="I265" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C266" s="14" t="s">
         <v>9</v>
@@ -9275,15 +9297,15 @@
         <v>1.2096122000000001E-2</v>
       </c>
       <c r="I266" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B267" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C267" s="14" t="s">
         <v>9</v>
@@ -9305,15 +9327,15 @@
         <v>2.1645692000000001E-2</v>
       </c>
       <c r="I267" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C268" s="14" t="s">
         <v>9</v>
@@ -9335,15 +9357,15 @@
         <v>4.1063151000000006E-2</v>
       </c>
       <c r="I268" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C269" s="14" t="s">
         <v>9</v>
@@ -9365,15 +9387,15 @@
         <v>6.6846989999999995E-2</v>
       </c>
       <c r="I269" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C270" s="14" t="s">
         <v>9</v>
@@ -9395,15 +9417,15 @@
         <v>9.1675871999999992E-2</v>
       </c>
       <c r="I270" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C271" s="14" t="s">
         <v>9</v>
@@ -9425,15 +9447,15 @@
         <v>0.12096122000000001</v>
       </c>
       <c r="I271" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C272" s="14" t="s">
         <v>9</v>
@@ -9455,15 +9477,15 @@
         <v>0.15597631000000001</v>
       </c>
       <c r="I272" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B273" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C273" s="14" t="s">
         <v>9</v>
@@ -9485,15 +9507,15 @@
         <v>0.17507545000000002</v>
       </c>
       <c r="I273" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>9</v>
@@ -9515,15 +9537,15 @@
         <v>3.1831900000000002E-3</v>
       </c>
       <c r="I274" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>9</v>
@@ -9545,15 +9567,15 @@
         <v>9.5495700000000003E-3</v>
       </c>
       <c r="I275" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C276" s="8" t="s">
         <v>9</v>
@@ -9575,15 +9597,15 @@
         <v>3.5015090000000006E-2</v>
       </c>
       <c r="I276" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>9</v>
@@ -9605,15 +9627,15 @@
         <v>7.6396560000000002E-2</v>
       </c>
       <c r="I277" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>9</v>
@@ -9635,15 +9657,15 @@
         <v>0.12350777200000002</v>
       </c>
       <c r="I278" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>9</v>
@@ -9665,15 +9687,15 @@
         <v>0.16870907000000002</v>
       </c>
       <c r="I279" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B280" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C280" s="8" t="s">
         <v>9</v>
@@ -9695,15 +9717,15 @@
         <v>0.21964011</v>
       </c>
       <c r="I280" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C281" s="8" t="s">
         <v>9</v>
@@ -9725,15 +9747,15 @@
         <v>0.24224075900000003</v>
       </c>
       <c r="I281" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B282" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C282" s="33" t="s">
         <v>9</v>
@@ -9755,15 +9777,15 @@
         <v>6.0480610000000004E-3</v>
       </c>
       <c r="I282" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B283" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C283" s="33" t="s">
         <v>9</v>
@@ -9785,15 +9807,15 @@
         <v>1.5279312000000001E-2</v>
       </c>
       <c r="I283" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B284" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C284" s="33" t="s">
         <v>9</v>
@@ -9815,15 +9837,15 @@
         <v>3.4696771000000001E-2</v>
       </c>
       <c r="I284" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B285" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C285" s="33" t="s">
         <v>9</v>
@@ -9845,15 +9867,15 @@
         <v>5.0612721000000006E-2</v>
       </c>
       <c r="I285" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B286" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C286" s="33" t="s">
         <v>9</v>
@@ -9875,15 +9897,15 @@
         <v>6.9393542000000003E-2</v>
       </c>
       <c r="I286" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B287" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C287" s="33" t="s">
         <v>19</v>
@@ -9905,15 +9927,15 @@
         <v>9.4540742999999997E-2</v>
       </c>
       <c r="I287" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B288" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C288" s="33" t="s">
         <v>19</v>
@@ -9935,15 +9957,15 @@
         <v>0.12064290100000001</v>
       </c>
       <c r="I288" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B289" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C289" s="33" t="s">
         <v>19</v>
@@ -9965,195 +9987,968 @@
         <v>0.13655885100000001</v>
       </c>
       <c r="I289" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A290" s="40"/>
-      <c r="B290" s="41"/>
-      <c r="C290" s="40"/>
-      <c r="D290" s="42"/>
-      <c r="E290" s="40"/>
-      <c r="F290" s="43"/>
-      <c r="G290" s="40"/>
-      <c r="H290" s="44"/>
-      <c r="I290" s="45"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A291" s="40"/>
-      <c r="B291" s="41"/>
-      <c r="C291" s="40"/>
-      <c r="D291" s="42"/>
-      <c r="E291" s="40"/>
-      <c r="F291" s="43"/>
-      <c r="G291" s="40"/>
-      <c r="H291" s="44"/>
-      <c r="I291" s="45"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A292" s="40"/>
-      <c r="B292" s="41"/>
-      <c r="C292" s="40"/>
-      <c r="D292" s="42"/>
-      <c r="E292" s="40"/>
-      <c r="F292" s="43"/>
-      <c r="G292" s="40"/>
-      <c r="H292" s="44"/>
-      <c r="I292" s="45"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A293" s="40"/>
-      <c r="B293" s="41"/>
-      <c r="C293" s="40"/>
-      <c r="D293" s="42"/>
-      <c r="E293" s="40"/>
-      <c r="F293" s="43"/>
-      <c r="G293" s="40"/>
-      <c r="H293" s="44"/>
-      <c r="I293" s="45"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A294" s="40"/>
-      <c r="B294" s="41"/>
-      <c r="C294" s="40"/>
-      <c r="D294" s="42"/>
-      <c r="E294" s="40"/>
-      <c r="F294" s="43"/>
-      <c r="G294" s="40"/>
-      <c r="H294" s="44"/>
-      <c r="I294" s="45"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="40"/>
-      <c r="B295" s="41"/>
-      <c r="C295" s="40"/>
-      <c r="D295" s="42"/>
-      <c r="E295" s="40"/>
-      <c r="F295" s="43"/>
-      <c r="G295" s="40"/>
-      <c r="H295" s="44"/>
-      <c r="I295" s="45"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A296" s="40"/>
-      <c r="B296" s="41"/>
-      <c r="C296" s="40"/>
-      <c r="D296" s="42"/>
-      <c r="E296" s="40"/>
-      <c r="F296" s="43"/>
-      <c r="G296" s="40"/>
-      <c r="H296" s="44"/>
-      <c r="I296" s="45"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="40"/>
-      <c r="B297" s="41"/>
-      <c r="C297" s="40"/>
-      <c r="D297" s="42"/>
-      <c r="E297" s="40"/>
-      <c r="F297" s="43"/>
-      <c r="G297" s="40"/>
-      <c r="H297" s="44"/>
-      <c r="I297" s="45"/>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A298" s="46"/>
-      <c r="B298" s="47"/>
-      <c r="C298" s="48"/>
-      <c r="D298" s="46"/>
-      <c r="E298" s="48"/>
-      <c r="F298" s="49"/>
-      <c r="G298" s="48"/>
-      <c r="H298" s="50"/>
-      <c r="I298" s="51"/>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A299" s="46"/>
-      <c r="B299" s="47"/>
-      <c r="C299" s="48"/>
-      <c r="D299" s="46"/>
-      <c r="E299" s="48"/>
-      <c r="F299" s="49"/>
-      <c r="G299" s="48"/>
-      <c r="H299" s="50"/>
-      <c r="I299" s="51"/>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A300" s="46"/>
-      <c r="B300" s="47"/>
-      <c r="C300" s="48"/>
-      <c r="D300" s="46"/>
-      <c r="E300" s="48"/>
-      <c r="F300" s="49"/>
-      <c r="G300" s="48"/>
-      <c r="H300" s="50"/>
-      <c r="I300" s="51"/>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="46"/>
-      <c r="B301" s="47"/>
-      <c r="C301" s="48"/>
-      <c r="D301" s="46"/>
-      <c r="E301" s="48"/>
-      <c r="F301" s="49"/>
-      <c r="G301" s="48"/>
-      <c r="H301" s="50"/>
-      <c r="I301" s="51"/>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A302" s="46"/>
-      <c r="B302" s="47"/>
-      <c r="C302" s="48"/>
-      <c r="D302" s="46"/>
-      <c r="E302" s="48"/>
-      <c r="F302" s="49"/>
-      <c r="G302" s="48"/>
-      <c r="H302" s="50"/>
-      <c r="I302" s="51"/>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="46"/>
-      <c r="B303" s="47"/>
-      <c r="C303" s="48"/>
-      <c r="D303" s="46"/>
-      <c r="E303" s="48"/>
-      <c r="F303" s="49"/>
-      <c r="G303" s="48"/>
-      <c r="H303" s="50"/>
-      <c r="I303" s="51"/>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A304" s="46"/>
-      <c r="B304" s="47"/>
-      <c r="C304" s="48"/>
-      <c r="D304" s="46"/>
-      <c r="E304" s="48"/>
-      <c r="F304" s="49"/>
-      <c r="G304" s="48"/>
-      <c r="H304" s="50"/>
-      <c r="I304" s="51"/>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A305" s="46"/>
-      <c r="B305" s="47"/>
-      <c r="C305" s="48"/>
-      <c r="D305" s="46"/>
-      <c r="E305" s="48"/>
-      <c r="F305" s="49"/>
-      <c r="G305" s="48"/>
-      <c r="H305" s="50"/>
-      <c r="I305" s="51"/>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A306" s="52"/>
-      <c r="B306" s="52"/>
-      <c r="C306" s="52"/>
-      <c r="D306" s="52"/>
-      <c r="E306" s="52"/>
-      <c r="F306" s="53"/>
-      <c r="G306" s="52"/>
-      <c r="H306" s="54"/>
-      <c r="I306" s="52"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A290" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B290" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C290" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D290" s="18">
+        <v>60</v>
+      </c>
+      <c r="E290" s="20">
+        <v>0</v>
+      </c>
+      <c r="F290" s="21">
+        <v>0</v>
+      </c>
+      <c r="G290" s="18">
+        <v>55</v>
+      </c>
+      <c r="H290" s="22">
+        <f t="shared" si="9"/>
+        <v>1.7507545000000003E-2</v>
+      </c>
+      <c r="I290" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A291" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B291" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C291" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D291" s="18">
+        <v>60</v>
+      </c>
+      <c r="E291" s="20">
+        <v>1</v>
+      </c>
+      <c r="F291" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="G291" s="18">
+        <v>194</v>
+      </c>
+      <c r="H291" s="22">
+        <f t="shared" si="9"/>
+        <v>6.1753886000000008E-2</v>
+      </c>
+      <c r="I291" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A292" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B292" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C292" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D292" s="18">
+        <v>60</v>
+      </c>
+      <c r="E292" s="20">
+        <v>2</v>
+      </c>
+      <c r="F292" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G292" s="20">
+        <v>274</v>
+      </c>
+      <c r="H292" s="22">
+        <f t="shared" si="9"/>
+        <v>8.7219406000000013E-2</v>
+      </c>
+      <c r="I292" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A293" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B293" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C293" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D293" s="18">
+        <v>60</v>
+      </c>
+      <c r="E293" s="20">
+        <v>3</v>
+      </c>
+      <c r="F293" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="G293" s="20">
+        <v>415</v>
+      </c>
+      <c r="H293" s="22">
+        <f t="shared" si="9"/>
+        <v>0.13210238499999999</v>
+      </c>
+      <c r="I293" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A294" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B294" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C294" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D294" s="18">
+        <v>60</v>
+      </c>
+      <c r="E294" s="20">
+        <v>4</v>
+      </c>
+      <c r="F294" s="21">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G294" s="20">
+        <v>617</v>
+      </c>
+      <c r="H294" s="22">
+        <f t="shared" si="9"/>
+        <v>0.196402823</v>
+      </c>
+      <c r="I294" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A295" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B295" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C295" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" s="18">
+        <v>60</v>
+      </c>
+      <c r="E295" s="20">
+        <v>5</v>
+      </c>
+      <c r="F295" s="21">
+        <v>0.71</v>
+      </c>
+      <c r="G295" s="20">
+        <v>877</v>
+      </c>
+      <c r="H295" s="22">
+        <f t="shared" si="9"/>
+        <v>0.27916576300000001</v>
+      </c>
+      <c r="I295" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A296" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B296" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C296" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D296" s="18">
+        <v>60</v>
+      </c>
+      <c r="E296" s="20">
+        <v>7</v>
+      </c>
+      <c r="F296" s="21">
+        <v>0.88</v>
+      </c>
+      <c r="G296" s="20">
+        <v>1136</v>
+      </c>
+      <c r="H296" s="22">
+        <f t="shared" ref="H296" si="10">G296/1000*0.318319</f>
+        <v>0.36161038400000001</v>
+      </c>
+      <c r="I296" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A297" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B297" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C297" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D297" s="18">
+        <v>60</v>
+      </c>
+      <c r="E297" s="20">
+        <v>10</v>
+      </c>
+      <c r="F297" s="21">
+        <v>0.99</v>
+      </c>
+      <c r="G297" s="20">
+        <v>1298</v>
+      </c>
+      <c r="H297" s="22">
+        <f t="shared" si="9"/>
+        <v>0.41317806200000001</v>
+      </c>
+      <c r="I297" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A298" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C298" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D298" s="12">
+        <v>60</v>
+      </c>
+      <c r="E298" s="14">
+        <v>0</v>
+      </c>
+      <c r="F298" s="15">
+        <v>0</v>
+      </c>
+      <c r="G298" s="14">
+        <v>65</v>
+      </c>
+      <c r="H298" s="16">
+        <f t="shared" ref="H298:H321" si="11">G298/1000*0.318319</f>
+        <v>2.0690735000000002E-2</v>
+      </c>
+      <c r="I298" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A299" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B299" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C299" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D299" s="12">
+        <v>60</v>
+      </c>
+      <c r="E299" s="14">
+        <v>1</v>
+      </c>
+      <c r="F299" s="15">
+        <v>0.16</v>
+      </c>
+      <c r="G299" s="14">
+        <v>90</v>
+      </c>
+      <c r="H299" s="16">
+        <f t="shared" si="11"/>
+        <v>2.8648710000000001E-2</v>
+      </c>
+      <c r="I299" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A300" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C300" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D300" s="12">
+        <v>60</v>
+      </c>
+      <c r="E300" s="14">
+        <v>2</v>
+      </c>
+      <c r="F300" s="15">
+        <v>0.31</v>
+      </c>
+      <c r="G300" s="14">
+        <v>235</v>
+      </c>
+      <c r="H300" s="16">
+        <f t="shared" si="11"/>
+        <v>7.4804965000000001E-2</v>
+      </c>
+      <c r="I300" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A301" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B301" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C301" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D301" s="12">
+        <v>60</v>
+      </c>
+      <c r="E301" s="14">
+        <v>3</v>
+      </c>
+      <c r="F301" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="G301" s="14">
+        <v>375</v>
+      </c>
+      <c r="H301" s="16">
+        <f t="shared" si="11"/>
+        <v>0.11936962500000001</v>
+      </c>
+      <c r="I301" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A302" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B302" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C302" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D302" s="12">
+        <v>60</v>
+      </c>
+      <c r="E302" s="14">
+        <v>4</v>
+      </c>
+      <c r="F302" s="15">
+        <v>0.59</v>
+      </c>
+      <c r="G302" s="14">
+        <v>523</v>
+      </c>
+      <c r="H302" s="16">
+        <f t="shared" si="11"/>
+        <v>0.16648083700000002</v>
+      </c>
+      <c r="I302" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A303" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B303" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C303" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" s="12">
+        <v>60</v>
+      </c>
+      <c r="E303" s="14">
+        <v>5</v>
+      </c>
+      <c r="F303" s="15">
+        <v>0.72</v>
+      </c>
+      <c r="G303" s="14">
+        <v>696</v>
+      </c>
+      <c r="H303" s="16">
+        <f t="shared" si="11"/>
+        <v>0.22155002399999998</v>
+      </c>
+      <c r="I303" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A304" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C304" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D304" s="12">
+        <v>60</v>
+      </c>
+      <c r="E304" s="14">
+        <v>7</v>
+      </c>
+      <c r="F304" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="G304" s="14">
+        <v>995</v>
+      </c>
+      <c r="H304" s="16">
+        <f t="shared" si="11"/>
+        <v>0.31672740500000002</v>
+      </c>
+      <c r="I304" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A305" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B305" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C305" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D305" s="12">
+        <v>60</v>
+      </c>
+      <c r="E305" s="14">
+        <v>10</v>
+      </c>
+      <c r="F305" s="15">
+        <v>0.99</v>
+      </c>
+      <c r="G305" s="14">
+        <v>1257</v>
+      </c>
+      <c r="H305" s="16">
+        <f t="shared" si="11"/>
+        <v>0.40012698299999999</v>
+      </c>
+      <c r="I305" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A306" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C306" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D306" s="31">
+        <v>60</v>
+      </c>
+      <c r="E306" s="33">
+        <v>0</v>
+      </c>
+      <c r="F306" s="34">
+        <v>0</v>
+      </c>
+      <c r="G306" s="33">
+        <v>349</v>
+      </c>
+      <c r="H306" s="35">
+        <f t="shared" si="11"/>
+        <v>0.111093331</v>
+      </c>
+      <c r="I306" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A307" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B307" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C307" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D307" s="31">
+        <v>60</v>
+      </c>
+      <c r="E307" s="33">
+        <v>1</v>
+      </c>
+      <c r="F307" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="G307" s="33">
+        <v>488</v>
+      </c>
+      <c r="H307" s="35">
+        <f t="shared" si="11"/>
+        <v>0.15533967200000001</v>
+      </c>
+      <c r="I307" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A308" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B308" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C308" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D308" s="31">
+        <v>60</v>
+      </c>
+      <c r="E308" s="33">
+        <v>2</v>
+      </c>
+      <c r="F308" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="G308" s="33">
+        <v>668</v>
+      </c>
+      <c r="H308" s="35">
+        <f t="shared" si="11"/>
+        <v>0.21263709200000003</v>
+      </c>
+      <c r="I308" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A309" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B309" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C309" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D309" s="31">
+        <v>60</v>
+      </c>
+      <c r="E309" s="33">
+        <v>3</v>
+      </c>
+      <c r="F309" s="34">
+        <v>0.44</v>
+      </c>
+      <c r="G309" s="33">
+        <v>768</v>
+      </c>
+      <c r="H309" s="35">
+        <f t="shared" si="11"/>
+        <v>0.24446899200000002</v>
+      </c>
+      <c r="I309" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A310" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B310" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C310" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D310" s="31">
+        <v>60</v>
+      </c>
+      <c r="E310" s="33">
+        <v>4</v>
+      </c>
+      <c r="F310" s="34">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G310" s="33">
+        <v>878</v>
+      </c>
+      <c r="H310" s="35">
+        <f t="shared" si="11"/>
+        <v>0.27948408200000002</v>
+      </c>
+      <c r="I310" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A311" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B311" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C311" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D311" s="31">
+        <v>60</v>
+      </c>
+      <c r="E311" s="33">
+        <v>5</v>
+      </c>
+      <c r="F311" s="34">
+        <v>0.7</v>
+      </c>
+      <c r="G311" s="33">
+        <v>1018</v>
+      </c>
+      <c r="H311" s="35">
+        <f t="shared" si="11"/>
+        <v>0.324048742</v>
+      </c>
+      <c r="I311" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A312" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C312" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D312" s="31">
+        <v>60</v>
+      </c>
+      <c r="E312" s="33">
+        <v>7</v>
+      </c>
+      <c r="F312" s="34">
+        <v>0.87</v>
+      </c>
+      <c r="G312" s="33">
+        <v>1387</v>
+      </c>
+      <c r="H312" s="35">
+        <f t="shared" si="11"/>
+        <v>0.44150845300000002</v>
+      </c>
+      <c r="I312" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A313" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B313" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C313" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D313" s="31">
+        <v>60</v>
+      </c>
+      <c r="E313" s="33">
+        <v>10</v>
+      </c>
+      <c r="F313" s="34">
+        <v>0.98</v>
+      </c>
+      <c r="G313" s="33">
+        <v>1769</v>
+      </c>
+      <c r="H313" s="35">
+        <f t="shared" si="11"/>
+        <v>0.56310631099999997</v>
+      </c>
+      <c r="I313" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A314" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D314" s="6">
+        <v>60</v>
+      </c>
+      <c r="E314" s="8">
+        <v>0</v>
+      </c>
+      <c r="F314" s="9">
+        <v>0</v>
+      </c>
+      <c r="G314" s="8">
+        <v>-23</v>
+      </c>
+      <c r="H314" s="10">
+        <f t="shared" si="11"/>
+        <v>-7.3213370000000007E-3</v>
+      </c>
+      <c r="I314" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A315" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D315" s="6">
+        <v>60</v>
+      </c>
+      <c r="E315" s="8">
+        <v>1</v>
+      </c>
+      <c r="F315" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="G315" s="8">
+        <v>7</v>
+      </c>
+      <c r="H315" s="10">
+        <f t="shared" si="11"/>
+        <v>2.228233E-3</v>
+      </c>
+      <c r="I315" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A316" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D316" s="6">
+        <v>60</v>
+      </c>
+      <c r="E316" s="8">
+        <v>2</v>
+      </c>
+      <c r="F316" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G316" s="8">
+        <v>56</v>
+      </c>
+      <c r="H316" s="10">
+        <f t="shared" si="11"/>
+        <v>1.7825864E-2</v>
+      </c>
+      <c r="I316" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A317" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D317" s="6">
+        <v>60</v>
+      </c>
+      <c r="E317" s="8">
+        <v>3</v>
+      </c>
+      <c r="F317" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="G317" s="8">
+        <v>106</v>
+      </c>
+      <c r="H317" s="10">
+        <f t="shared" si="11"/>
+        <v>3.3741814000000002E-2</v>
+      </c>
+      <c r="I317" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A318" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D318" s="6">
+        <v>60</v>
+      </c>
+      <c r="E318" s="8">
+        <v>4</v>
+      </c>
+      <c r="F318" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G318" s="8">
+        <v>166</v>
+      </c>
+      <c r="H318" s="10">
+        <f t="shared" si="11"/>
+        <v>5.2840954000000002E-2</v>
+      </c>
+      <c r="I318" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A319" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D319" s="6">
+        <v>60</v>
+      </c>
+      <c r="E319" s="8">
+        <v>5</v>
+      </c>
+      <c r="F319" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="G319" s="8">
+        <v>227</v>
+      </c>
+      <c r="H319" s="10">
+        <f t="shared" si="11"/>
+        <v>7.2258413000000007E-2</v>
+      </c>
+      <c r="I319" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A320" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D320" s="6">
+        <v>60</v>
+      </c>
+      <c r="E320" s="8">
+        <v>7</v>
+      </c>
+      <c r="F320" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="G320" s="8">
+        <v>316</v>
+      </c>
+      <c r="H320" s="10">
+        <f t="shared" si="11"/>
+        <v>0.100588804</v>
+      </c>
+      <c r="I320" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A321" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321" s="6">
+        <v>60</v>
+      </c>
+      <c r="E321" s="8">
+        <v>10</v>
+      </c>
+      <c r="F321" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="G321" s="8">
+        <v>377</v>
+      </c>
+      <c r="H321" s="10">
+        <f t="shared" si="11"/>
+        <v>0.120006263</v>
+      </c>
+      <c r="I321" s="11" t="s">
+        <v>140</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -10169,7 +10964,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C117E7FB-486F-48B6-8752-BC50C1B73335}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10180,18 +10975,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F252649E-4352-49A5-A081-F3BFF4884345}">
   <dimension ref="A1:C145"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
+    <col min="2" max="2" width="48.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="38" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
         <v>60</v>
       </c>
@@ -10200,7 +10995,7 @@
       </c>
       <c r="C2" s="37"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="37" t="s">
         <v>15</v>
       </c>
@@ -10209,7 +11004,7 @@
       </c>
       <c r="C3" s="37"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
         <v>56</v>
       </c>
@@ -10217,7 +11012,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
@@ -10225,23 +11020,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
         <v>58</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="37" t="s">
         <v>61</v>
       </c>
@@ -10249,7 +11044,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="37" t="s">
         <v>62</v>
       </c>
@@ -10257,7 +11052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
         <v>63</v>
       </c>
@@ -10265,627 +11060,635 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
         <v>64</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="B17" s="37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>84</v>
-      </c>
       <c r="B18" s="37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="37" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B24" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="39" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="37" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="37" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="B28" s="37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
-      <c r="B33" s="37"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
       <c r="B34" s="37"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="37"/>
       <c r="B35" s="37"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="37"/>
       <c r="B36" s="37"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="37"/>
       <c r="B37" s="37"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="37"/>
       <c r="B38" s="37"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="37"/>
       <c r="B39" s="37"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="37"/>
       <c r="B40" s="37"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="37"/>
       <c r="B41" s="37"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="37"/>
       <c r="B42" s="37"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="37"/>
       <c r="B43" s="37"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="37"/>
       <c r="B44" s="37"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="37"/>
       <c r="B45" s="37"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="37"/>
       <c r="B46" s="37"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="37"/>
       <c r="B47" s="37"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="37"/>
       <c r="B48" s="37"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="37"/>
       <c r="B49" s="37"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="37"/>
       <c r="B50" s="37"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="37"/>
       <c r="B51" s="37"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="37"/>
       <c r="B52" s="37"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="37"/>
       <c r="B53" s="37"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="37"/>
       <c r="B54" s="37"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="37"/>
       <c r="B55" s="37"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="37"/>
       <c r="B56" s="37"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="37"/>
       <c r="B57" s="37"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="37"/>
       <c r="B58" s="37"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="37"/>
       <c r="B59" s="37"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
       <c r="B60" s="37"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
       <c r="B61" s="37"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="37"/>
       <c r="B62" s="37"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="37"/>
       <c r="B63" s="37"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="37"/>
       <c r="B64" s="37"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="37"/>
       <c r="B65" s="37"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="37"/>
       <c r="B66" s="37"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="37"/>
       <c r="B67" s="37"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="37"/>
       <c r="B68" s="37"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="37"/>
       <c r="B69" s="37"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="37"/>
       <c r="B70" s="37"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="37"/>
       <c r="B71" s="37"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="37"/>
       <c r="B72" s="37"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="37"/>
       <c r="B73" s="37"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="37"/>
       <c r="B74" s="37"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="37"/>
       <c r="B75" s="37"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="37"/>
       <c r="B76" s="37"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="37"/>
       <c r="B77" s="37"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="37"/>
       <c r="B78" s="37"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="37"/>
       <c r="B79" s="37"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="37"/>
       <c r="B80" s="37"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="37"/>
       <c r="B81" s="37"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="37"/>
       <c r="B82" s="37"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="37"/>
       <c r="B83" s="37"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="37"/>
       <c r="B84" s="37"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="37"/>
       <c r="B85" s="37"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="37"/>
       <c r="B86" s="37"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="37"/>
       <c r="B87" s="37"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="37"/>
       <c r="B88" s="37"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="37"/>
       <c r="B89" s="37"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="37"/>
       <c r="B90" s="37"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="37"/>
       <c r="B91" s="37"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="37"/>
       <c r="B92" s="37"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="37"/>
       <c r="B93" s="37"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="37"/>
       <c r="B94" s="37"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="37"/>
       <c r="B95" s="37"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="37"/>
       <c r="B96" s="37"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="37"/>
       <c r="B97" s="37"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="37"/>
       <c r="B98" s="37"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="37"/>
       <c r="B99" s="37"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="37"/>
       <c r="B100" s="37"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="37"/>
       <c r="B101" s="37"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="37"/>
       <c r="B102" s="37"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="37"/>
       <c r="B103" s="37"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="37"/>
       <c r="B104" s="37"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="37"/>
       <c r="B105" s="37"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="37"/>
       <c r="B106" s="37"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="37"/>
       <c r="B107" s="37"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="37"/>
       <c r="B108" s="37"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="37"/>
       <c r="B109" s="37"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="37"/>
       <c r="B110" s="37"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="37"/>
       <c r="B111" s="37"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="37"/>
       <c r="B112" s="37"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="37"/>
       <c r="B113" s="37"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="37"/>
       <c r="B114" s="37"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="37"/>
       <c r="B115" s="37"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="37"/>
       <c r="B116" s="37"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="37"/>
       <c r="B117" s="37"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="37"/>
       <c r="B118" s="37"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="37"/>
       <c r="B119" s="37"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="37"/>
       <c r="B120" s="37"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="37"/>
       <c r="B121" s="37"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="37"/>
       <c r="B122" s="37"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="37"/>
       <c r="B123" s="37"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="37"/>
       <c r="B124" s="37"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="37"/>
       <c r="B125" s="37"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="37"/>
       <c r="B126" s="37"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="37"/>
       <c r="B127" s="37"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="37"/>
       <c r="B128" s="37"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="37"/>
       <c r="B129" s="37"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="37"/>
       <c r="B130" s="37"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="37"/>
       <c r="B131" s="37"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="37"/>
       <c r="B132" s="37"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="37"/>
       <c r="B133" s="37"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="37"/>
       <c r="B134" s="37"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="37"/>
       <c r="B135" s="37"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="37"/>
       <c r="B136" s="37"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="37"/>
       <c r="B137" s="37"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="37"/>
       <c r="B138" s="37"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="37"/>
       <c r="B139" s="37"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="37"/>
       <c r="B140" s="37"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="37"/>
       <c r="B141" s="37"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="37"/>
       <c r="B142" s="37"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="37"/>
       <c r="B143" s="37"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="37"/>
       <c r="B144" s="37"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="37"/>
       <c r="B145" s="37"/>
     </row>
